--- a/output/Data and Chart Outputs/jordan_peak_load_daily.xlsx
+++ b/output/Data and Chart Outputs/jordan_peak_load_daily.xlsx
@@ -195,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$C$2:$C$142</f>
+              <f>'Chart'!$C$2:$C$280</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$142</f>
+              <f>'Chart'!$B$2:$B$280</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -332,12 +332,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Monthly maximum'!$A$2:$A$6</f>
+              <f>'Chart - Monthly maximum'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Monthly maximum'!$B$2:$B$6</f>
+              <f>'Chart - Monthly maximum'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -870,1164 +870,2303 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46113</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>3710</v>
+        <v>3390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apr/26</t>
+          <t>Sep/25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46114</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>3760</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46117</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>3605</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46118</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>3590</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46119</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>3610</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46120</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>3740</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46121</v>
+        <v>45921</v>
       </c>
       <c r="B8" t="n">
-        <v>3660</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46124</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>3600</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46125</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>3560</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46126</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>3480</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46127</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>3340</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46128</v>
+        <v>45928</v>
       </c>
       <c r="B13" t="n">
-        <v>3250</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46131</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>3210</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46132</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>3230</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46133</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>3300</v>
+        <v>3320</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Oct/25</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46134</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>3310</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46135</v>
+        <v>45935</v>
       </c>
       <c r="B18" t="n">
-        <v>3280</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46138</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>3170</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46139</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>3255</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46140</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>3190</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46141</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>3200</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46145</v>
+        <v>45942</v>
       </c>
       <c r="B23" t="n">
-        <v>3180</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>May/26</t>
-        </is>
+        <v>3250</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46146</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>3190</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46147</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>3270</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46148</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>3380</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46149</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>3350</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46152</v>
+        <v>45949</v>
       </c>
       <c r="B28" t="n">
-        <v>3230</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46153</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>3210</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46154</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>3250</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46155</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>3270</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46156</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>3280</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46159</v>
+        <v>45956</v>
       </c>
       <c r="B33" t="n">
-        <v>3200</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46160</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>3300</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46161</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>3390</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46162</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>3350</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46163</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>3285</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46166</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>3220</v>
+        <v>3150</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nov/25</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46173</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>3030</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46174</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Jun/26</t>
-        </is>
+        <v>3200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46175</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>3300</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46176</v>
+        <v>45970</v>
       </c>
       <c r="B42" t="n">
-        <v>3330</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46177</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>3330</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46180</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>3380</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46181</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>3440</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46182</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>3425</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46183</v>
+        <v>45977</v>
       </c>
       <c r="B47" t="n">
-        <v>3460</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46184</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>3510</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46187</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>3365</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46188</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46190</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>3435</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46191</v>
+        <v>45984</v>
       </c>
       <c r="B52" t="n">
-        <v>3550</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46194</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>3470</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46195</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>3590</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46196</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>3560</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46197</v>
+        <v>45988</v>
       </c>
       <c r="B56" t="n">
-        <v>3450</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46198</v>
+        <v>45991</v>
       </c>
       <c r="B57" t="n">
-        <v>3490</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46201</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>3490</v>
+        <v>3460</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Dec/25</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46202</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>3585</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46203</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>3630</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46204</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>3610</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Jul/26</t>
-        </is>
+        <v>3520</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46205</v>
+        <v>45998</v>
       </c>
       <c r="B62" t="n">
-        <v>3630</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46208</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>3570</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46209</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>3640</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46210</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>3630</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46211</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>3610</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46212</v>
+        <v>46005</v>
       </c>
       <c r="B67" t="n">
-        <v>3540</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46215</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>3570</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46217</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>3730</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46218</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>3780</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46219</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>3780</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46222</v>
+        <v>46012</v>
       </c>
       <c r="B72" t="n">
-        <v>3740</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46223</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>3880</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46224</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>3870</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46225</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>3890</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46226</v>
+        <v>46019</v>
       </c>
       <c r="B76" t="n">
-        <v>4020</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46229</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>3735</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46230</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>3730</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46232</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>3770</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46233</v>
+        <v>46026</v>
       </c>
       <c r="B80" t="n">
-        <v>3880</v>
+        <v>4040</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46236</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>4160</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Aug/26</t>
-        </is>
+        <v>4175</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46237</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>4290</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46238</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>4140</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46239</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>4220</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46240</v>
+        <v>46033</v>
       </c>
       <c r="B85" t="n">
-        <v>4180</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46243</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>3990</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46244</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>3970</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46245</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>4020</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46246</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>4040</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46247</v>
+        <v>46040</v>
       </c>
       <c r="B90" t="n">
-        <v>4070</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46250</v>
+        <v>46041</v>
       </c>
       <c r="B91" t="n">
-        <v>3930</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46251</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>3755</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46252</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>3740</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46253</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>3860</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46254</v>
+        <v>46047</v>
       </c>
       <c r="B95" t="n">
-        <v>4050</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46255</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>3850</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46256</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>4120</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46257</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>4030</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46258</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>3990</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46259</v>
+        <v>46054</v>
       </c>
       <c r="B100" t="n">
-        <v>3880</v>
+        <v>3745</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Feb/26</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46260</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>4100</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46261</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>4020</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46262</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>3600</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46263</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>3820</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46264</v>
+        <v>46061</v>
       </c>
       <c r="B105" t="n">
-        <v>3660</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>3730</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46266</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>3845</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Sep/26</t>
-        </is>
+        <v>3430</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46267</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>3975</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46270</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>3730</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46271</v>
+        <v>46068</v>
       </c>
       <c r="B110" t="n">
-        <v>3680</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46272</v>
+        <v>46069</v>
       </c>
       <c r="B111" t="n">
-        <v>3830</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46273</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>3800</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46274</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>3720</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>3560</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46276</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>3320</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46277</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>3800</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46278</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>3810</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46279</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>3820</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46280</v>
+        <v>46082</v>
       </c>
       <c r="B119" t="n">
-        <v>3830</v>
+        <v>4070</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46281</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>3900</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46282</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>3730</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46283</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>3210</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46284</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>3580</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46285</v>
+        <v>46089</v>
       </c>
       <c r="B124" t="n">
-        <v>3575</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46286</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>3650</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46287</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>3630</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46288</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>3590</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46289</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46290</v>
+        <v>46096</v>
       </c>
       <c r="B129" t="n">
-        <v>3100</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46291</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>3500</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46292</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>3440</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46293</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>3450</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46294</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>3400</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46295</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>3410</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46296</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>3230</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Oct/26</t>
-        </is>
+        <v>3760</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46297</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>2880</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46298</v>
+        <v>46110</v>
       </c>
       <c r="B137" t="n">
-        <v>3320</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46299</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>3330</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46300</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>3280</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46301</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>3270</v>
+        <v>3710</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Apr/26</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46302</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>3300</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B148" t="n">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B149" t="n">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B151" t="n">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B153" t="n">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B154" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B155" t="n">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B156" t="n">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3255</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3180</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>May/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B162" t="n">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B163" t="n">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B164" t="n">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B165" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B169" t="n">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B170" t="n">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B171" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B172" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B174" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B175" t="n">
+        <v>3285</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B176" t="n">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B177" t="n">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B179" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B180" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B181" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>3425</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>3460</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B187" t="n">
+        <v>3365</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B188" t="n">
+        <v>3425</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3470</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B193" t="n">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B194" t="n">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B196" t="n">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B197" t="n">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B199" t="n">
+        <v>3610</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B200" t="n">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B201" t="n">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B203" t="n">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B205" t="n">
+        <v>3540</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B206" t="n">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B207" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B208" t="n">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B209" t="n">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B212" t="n">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B214" t="n">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B215" t="n">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B216" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B217" t="n">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B218" t="n">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4160</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Aug/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B220" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B221" t="n">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B222" t="n">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B223" t="n">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B224" t="n">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B225" t="n">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B229" t="n">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B230" t="n">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B231" t="n">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B232" t="n">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B233" t="n">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B235" t="n">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B236" t="n">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B237" t="n">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B238" t="n">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B239" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B240" t="n">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B241" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B242" t="n">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B244" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3845</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Sep/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B246" t="n">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B248" t="n">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B249" t="n">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B250" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B251" t="n">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B256" t="n">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B257" t="n">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B258" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B260" t="n">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B261" t="n">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B266" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B267" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B268" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B269" t="n">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B270" t="n">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B271" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B273" t="n">
+        <v>3230</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Oct/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B274" t="n">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B275" t="n">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B276" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B277" t="n">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B278" t="n">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B279" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="n">
         <v>46305</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B280" t="n">
         <v>3410</v>
       </c>
     </row>
@@ -2043,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2063,41 +3202,81 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46113</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>3760</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46174</v>
+        <v>45962</v>
       </c>
       <c r="B3" t="n">
-        <v>3630</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46204</v>
+        <v>45992</v>
       </c>
       <c r="B4" t="n">
-        <v>4020</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46235</v>
+        <v>46023</v>
       </c>
       <c r="B5" t="n">
-        <v>4290</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>46266</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B11" t="n">
         <v>3975</v>
       </c>
     </row>
@@ -2113,7 +3292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2145,13 +3324,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46113</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>3710</v>
+        <v>3390</v>
       </c>
       <c r="C2" t="n">
-        <v>3710</v>
+        <v>3390</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2161,13 +3340,13 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46114</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>3760</v>
+        <v>3380</v>
       </c>
       <c r="C3" t="n">
-        <v>3760</v>
+        <v>3380</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2177,13 +3356,13 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46117</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>3605</v>
+        <v>3560</v>
       </c>
       <c r="C4" t="n">
-        <v>3605</v>
+        <v>3560</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2193,13 +3372,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46118</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>3590</v>
+        <v>3545</v>
       </c>
       <c r="C5" t="n">
-        <v>3590</v>
+        <v>3545</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2209,13 +3388,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46119</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>3610</v>
+        <v>3500</v>
       </c>
       <c r="C6" t="n">
-        <v>3610</v>
+        <v>3500</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2225,13 +3404,13 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46120</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>3740</v>
+        <v>3460</v>
       </c>
       <c r="C7" t="n">
-        <v>3740</v>
+        <v>3460</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2241,13 +3420,13 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46121</v>
+        <v>45921</v>
       </c>
       <c r="B8" t="n">
-        <v>3660</v>
+        <v>3340</v>
       </c>
       <c r="C8" t="n">
-        <v>3660</v>
+        <v>3340</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2257,13 +3436,13 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46124</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>3600</v>
+        <v>3420</v>
       </c>
       <c r="C9" t="n">
-        <v>3600</v>
+        <v>3420</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2273,13 +3452,13 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46125</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>3560</v>
+        <v>3480</v>
       </c>
       <c r="C10" t="n">
-        <v>3560</v>
+        <v>3480</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2289,13 +3468,13 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46126</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>3480</v>
+        <v>3545</v>
       </c>
       <c r="C11" t="n">
-        <v>3480</v>
+        <v>3545</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2305,13 +3484,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46127</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>3340</v>
+        <v>3410</v>
       </c>
       <c r="C12" t="n">
-        <v>3340</v>
+        <v>3410</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2321,13 +3500,13 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46128</v>
+        <v>45928</v>
       </c>
       <c r="B13" t="n">
-        <v>3250</v>
+        <v>3300</v>
       </c>
       <c r="C13" t="n">
-        <v>3250</v>
+        <v>3300</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2337,13 +3516,13 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46131</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>3210</v>
+        <v>3400</v>
       </c>
       <c r="C14" t="n">
-        <v>3210</v>
+        <v>3400</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2353,13 +3532,13 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46132</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>3230</v>
+        <v>3400</v>
       </c>
       <c r="C15" t="n">
-        <v>3230</v>
+        <v>3400</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2369,13 +3548,13 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46133</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="C16" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2385,13 +3564,13 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46134</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>3310</v>
+        <v>3250</v>
       </c>
       <c r="C17" t="n">
-        <v>3310</v>
+        <v>3250</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2401,13 +3580,13 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46135</v>
+        <v>45935</v>
       </c>
       <c r="B18" t="n">
-        <v>3280</v>
+        <v>3410</v>
       </c>
       <c r="C18" t="n">
-        <v>3280</v>
+        <v>3410</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2417,13 +3596,13 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46138</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>3170</v>
+        <v>3370</v>
       </c>
       <c r="C19" t="n">
-        <v>3170</v>
+        <v>3370</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2433,13 +3612,13 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46139</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>3255</v>
+        <v>3260</v>
       </c>
       <c r="C20" t="n">
-        <v>3255</v>
+        <v>3260</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2449,13 +3628,13 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46140</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>3190</v>
+        <v>3260</v>
       </c>
       <c r="C21" t="n">
-        <v>3190</v>
+        <v>3260</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2465,13 +3644,13 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46141</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>3200</v>
+        <v>3230</v>
       </c>
       <c r="C22" t="n">
-        <v>3200</v>
+        <v>3230</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2481,13 +3660,13 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46145</v>
+        <v>45942</v>
       </c>
       <c r="B23" t="n">
-        <v>3180</v>
+        <v>3250</v>
       </c>
       <c r="C23" t="n">
-        <v>3180</v>
+        <v>3250</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2497,13 +3676,13 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46146</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>3190</v>
+        <v>3180</v>
       </c>
       <c r="C24" t="n">
-        <v>3190</v>
+        <v>3180</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2513,13 +3692,13 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46147</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>3270</v>
+        <v>3180</v>
       </c>
       <c r="C25" t="n">
-        <v>3270</v>
+        <v>3180</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2529,13 +3708,13 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46148</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>3380</v>
+        <v>3180</v>
       </c>
       <c r="C26" t="n">
-        <v>3380</v>
+        <v>3180</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2545,13 +3724,13 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46149</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>3350</v>
+        <v>3180</v>
       </c>
       <c r="C27" t="n">
-        <v>3350</v>
+        <v>3180</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2561,13 +3740,13 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46152</v>
+        <v>45949</v>
       </c>
       <c r="B28" t="n">
-        <v>3230</v>
+        <v>3205</v>
       </c>
       <c r="C28" t="n">
-        <v>3230</v>
+        <v>3205</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2577,13 +3756,13 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46153</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>3210</v>
+        <v>3170</v>
       </c>
       <c r="C29" t="n">
-        <v>3210</v>
+        <v>3170</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2593,13 +3772,13 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46154</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>3250</v>
+        <v>3130</v>
       </c>
       <c r="C30" t="n">
-        <v>3250</v>
+        <v>3130</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2609,13 +3788,13 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46155</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>3270</v>
+        <v>3200</v>
       </c>
       <c r="C31" t="n">
-        <v>3270</v>
+        <v>3200</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2625,13 +3804,13 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46156</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>3280</v>
+        <v>3260</v>
       </c>
       <c r="C32" t="n">
-        <v>3280</v>
+        <v>3260</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2641,13 +3820,13 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46159</v>
+        <v>45956</v>
       </c>
       <c r="B33" t="n">
-        <v>3200</v>
+        <v>3170</v>
       </c>
       <c r="C33" t="n">
-        <v>3200</v>
+        <v>3170</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2657,13 +3836,13 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46160</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>3300</v>
+        <v>3170</v>
       </c>
       <c r="C34" t="n">
-        <v>3300</v>
+        <v>3170</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2673,13 +3852,13 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46161</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>3390</v>
+        <v>3190</v>
       </c>
       <c r="C35" t="n">
-        <v>3390</v>
+        <v>3190</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2689,13 +3868,13 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46162</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>3350</v>
+        <v>3180</v>
       </c>
       <c r="C36" t="n">
-        <v>3350</v>
+        <v>3180</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2705,13 +3884,13 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46163</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>3285</v>
+        <v>3170</v>
       </c>
       <c r="C37" t="n">
-        <v>3285</v>
+        <v>3170</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2721,13 +3900,13 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46166</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>3220</v>
+        <v>3150</v>
       </c>
       <c r="C38" t="n">
-        <v>3220</v>
+        <v>3150</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2737,13 +3916,13 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46173</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>3030</v>
+        <v>3190</v>
       </c>
       <c r="C39" t="n">
-        <v>3030</v>
+        <v>3190</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2753,13 +3932,13 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46174</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="C40" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2769,13 +3948,13 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46175</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>3300</v>
+        <v>3240</v>
       </c>
       <c r="C41" t="n">
-        <v>3300</v>
+        <v>3240</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2785,13 +3964,13 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46176</v>
+        <v>45970</v>
       </c>
       <c r="B42" t="n">
-        <v>3330</v>
+        <v>3160</v>
       </c>
       <c r="C42" t="n">
-        <v>3330</v>
+        <v>3160</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2801,13 +3980,13 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46177</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>3330</v>
+        <v>3150</v>
       </c>
       <c r="C43" t="n">
-        <v>3330</v>
+        <v>3150</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2817,13 +3996,13 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46180</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>3380</v>
+        <v>3150</v>
       </c>
       <c r="C44" t="n">
-        <v>3380</v>
+        <v>3150</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2833,13 +4012,13 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46181</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>3440</v>
+        <v>3190</v>
       </c>
       <c r="C45" t="n">
-        <v>3440</v>
+        <v>3190</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2849,13 +4028,13 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46182</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>3425</v>
+        <v>3150</v>
       </c>
       <c r="C46" t="n">
-        <v>3425</v>
+        <v>3150</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2865,13 +4044,13 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46183</v>
+        <v>45977</v>
       </c>
       <c r="B47" t="n">
-        <v>3460</v>
+        <v>3360</v>
       </c>
       <c r="C47" t="n">
-        <v>3460</v>
+        <v>3360</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2881,13 +4060,13 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46184</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>3510</v>
+        <v>3320</v>
       </c>
       <c r="C48" t="n">
-        <v>3510</v>
+        <v>3320</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2897,13 +4076,13 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46187</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>3365</v>
+        <v>3360</v>
       </c>
       <c r="C49" t="n">
-        <v>3365</v>
+        <v>3360</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2913,13 +4092,13 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46188</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="C50" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2929,13 +4108,13 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46190</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>3435</v>
+        <v>3390</v>
       </c>
       <c r="C51" t="n">
-        <v>3435</v>
+        <v>3390</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2945,13 +4124,13 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46191</v>
+        <v>45984</v>
       </c>
       <c r="B52" t="n">
-        <v>3550</v>
+        <v>3280</v>
       </c>
       <c r="C52" t="n">
-        <v>3550</v>
+        <v>3280</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2961,13 +4140,13 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46194</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>3470</v>
+        <v>3230</v>
       </c>
       <c r="C53" t="n">
-        <v>3470</v>
+        <v>3230</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2977,13 +4156,13 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46195</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>3590</v>
+        <v>3260</v>
       </c>
       <c r="C54" t="n">
-        <v>3590</v>
+        <v>3260</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2993,13 +4172,13 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>46196</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>3560</v>
+        <v>3370</v>
       </c>
       <c r="C55" t="n">
-        <v>3560</v>
+        <v>3370</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3009,13 +4188,13 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>46197</v>
+        <v>45988</v>
       </c>
       <c r="B56" t="n">
-        <v>3450</v>
+        <v>3370</v>
       </c>
       <c r="C56" t="n">
-        <v>3450</v>
+        <v>3370</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3025,13 +4204,13 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>46198</v>
+        <v>45991</v>
       </c>
       <c r="B57" t="n">
-        <v>3490</v>
+        <v>3360</v>
       </c>
       <c r="C57" t="n">
-        <v>3490</v>
+        <v>3360</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3041,13 +4220,13 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>46201</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>3490</v>
+        <v>3460</v>
       </c>
       <c r="C58" t="n">
-        <v>3490</v>
+        <v>3460</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3057,13 +4236,13 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>46202</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>3585</v>
+        <v>3490</v>
       </c>
       <c r="C59" t="n">
-        <v>3585</v>
+        <v>3490</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3073,13 +4252,13 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>46203</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>3630</v>
+        <v>3500</v>
       </c>
       <c r="C60" t="n">
-        <v>3630</v>
+        <v>3500</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3089,13 +4268,13 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>46204</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>3610</v>
+        <v>3520</v>
       </c>
       <c r="C61" t="n">
-        <v>3610</v>
+        <v>3520</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3105,13 +4284,13 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>46205</v>
+        <v>45998</v>
       </c>
       <c r="B62" t="n">
-        <v>3630</v>
+        <v>3410</v>
       </c>
       <c r="C62" t="n">
-        <v>3630</v>
+        <v>3410</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3121,13 +4300,13 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>46208</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>3570</v>
+        <v>3560</v>
       </c>
       <c r="C63" t="n">
-        <v>3570</v>
+        <v>3560</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3137,13 +4316,13 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>46209</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>3640</v>
+        <v>3700</v>
       </c>
       <c r="C64" t="n">
-        <v>3640</v>
+        <v>3700</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3153,13 +4332,13 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
-        <v>46210</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>3630</v>
+        <v>3750</v>
       </c>
       <c r="C65" t="n">
-        <v>3630</v>
+        <v>3750</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3169,13 +4348,13 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>46211</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>3610</v>
+        <v>3830</v>
       </c>
       <c r="C66" t="n">
-        <v>3610</v>
+        <v>3830</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3185,13 +4364,13 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>46212</v>
+        <v>46005</v>
       </c>
       <c r="B67" t="n">
-        <v>3540</v>
+        <v>3850</v>
       </c>
       <c r="C67" t="n">
-        <v>3540</v>
+        <v>3850</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3201,13 +4380,13 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>46215</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>3570</v>
+        <v>3830</v>
       </c>
       <c r="C68" t="n">
-        <v>3570</v>
+        <v>3830</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3217,13 +4396,13 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>46217</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>3730</v>
+        <v>3910</v>
       </c>
       <c r="C69" t="n">
-        <v>3730</v>
+        <v>3910</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3233,13 +4412,13 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>46218</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>3780</v>
+        <v>3980</v>
       </c>
       <c r="C70" t="n">
-        <v>3780</v>
+        <v>3980</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3249,13 +4428,13 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>46219</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>3780</v>
+        <v>4120</v>
       </c>
       <c r="C71" t="n">
-        <v>3780</v>
+        <v>4120</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3265,13 +4444,13 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
-        <v>46222</v>
+        <v>46012</v>
       </c>
       <c r="B72" t="n">
-        <v>3740</v>
+        <v>3870</v>
       </c>
       <c r="C72" t="n">
-        <v>3740</v>
+        <v>3870</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3281,13 +4460,13 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>46223</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>3880</v>
+        <v>3940</v>
       </c>
       <c r="C73" t="n">
-        <v>3880</v>
+        <v>3940</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3297,13 +4476,13 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>46224</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>3870</v>
+        <v>3950</v>
       </c>
       <c r="C74" t="n">
-        <v>3870</v>
+        <v>3950</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3313,13 +4492,13 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>46225</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>3890</v>
+        <v>3910</v>
       </c>
       <c r="C75" t="n">
-        <v>3890</v>
+        <v>3910</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3329,13 +4508,13 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>46226</v>
+        <v>46019</v>
       </c>
       <c r="B76" t="n">
-        <v>4020</v>
+        <v>4025</v>
       </c>
       <c r="C76" t="n">
-        <v>4020</v>
+        <v>4025</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3345,13 +4524,13 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>46229</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>3735</v>
+        <v>4100</v>
       </c>
       <c r="C77" t="n">
-        <v>3735</v>
+        <v>4100</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3361,13 +4540,13 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>46230</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>3730</v>
+        <v>4210</v>
       </c>
       <c r="C78" t="n">
-        <v>3730</v>
+        <v>4210</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3377,13 +4556,13 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>46232</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>3770</v>
+        <v>3960</v>
       </c>
       <c r="C79" t="n">
-        <v>3770</v>
+        <v>3960</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3393,13 +4572,13 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46233</v>
+        <v>46026</v>
       </c>
       <c r="B80" t="n">
-        <v>3880</v>
+        <v>4040</v>
       </c>
       <c r="C80" t="n">
-        <v>3880</v>
+        <v>4040</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3409,13 +4588,13 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46236</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>4160</v>
+        <v>4175</v>
       </c>
       <c r="C81" t="n">
-        <v>4160</v>
+        <v>4175</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3425,13 +4604,13 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46237</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>4290</v>
+        <v>4080</v>
       </c>
       <c r="C82" t="n">
-        <v>4290</v>
+        <v>4080</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3441,13 +4620,13 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>46238</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>4140</v>
+        <v>3950</v>
       </c>
       <c r="C83" t="n">
-        <v>4140</v>
+        <v>3950</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3457,13 +4636,13 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>46239</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>4220</v>
+        <v>3800</v>
       </c>
       <c r="C84" t="n">
-        <v>4220</v>
+        <v>3800</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3473,13 +4652,13 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>46240</v>
+        <v>46033</v>
       </c>
       <c r="B85" t="n">
-        <v>4180</v>
+        <v>3905</v>
       </c>
       <c r="C85" t="n">
-        <v>4180</v>
+        <v>3905</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3489,13 +4668,13 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>46243</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>3990</v>
+        <v>3860</v>
       </c>
       <c r="C86" t="n">
-        <v>3990</v>
+        <v>3860</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3505,13 +4684,13 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>46244</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>3970</v>
+        <v>4060</v>
       </c>
       <c r="C87" t="n">
-        <v>3970</v>
+        <v>4060</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3521,13 +4700,13 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>46245</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>4020</v>
+        <v>4340</v>
       </c>
       <c r="C88" t="n">
-        <v>4020</v>
+        <v>4340</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3537,13 +4716,13 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>46246</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>4040</v>
+        <v>4330</v>
       </c>
       <c r="C89" t="n">
-        <v>4040</v>
+        <v>4330</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3553,13 +4732,13 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>46247</v>
+        <v>46040</v>
       </c>
       <c r="B90" t="n">
-        <v>4070</v>
+        <v>4060</v>
       </c>
       <c r="C90" t="n">
-        <v>4070</v>
+        <v>4060</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3569,13 +4748,13 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
-        <v>46250</v>
+        <v>46041</v>
       </c>
       <c r="B91" t="n">
-        <v>3930</v>
+        <v>4310</v>
       </c>
       <c r="C91" t="n">
-        <v>3930</v>
+        <v>4310</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3585,13 +4764,13 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>46251</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>3755</v>
+        <v>3260</v>
       </c>
       <c r="C92" t="n">
-        <v>3755</v>
+        <v>3260</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3601,13 +4780,13 @@
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
-        <v>46252</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>3740</v>
+        <v>4350</v>
       </c>
       <c r="C93" t="n">
-        <v>3740</v>
+        <v>4350</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3617,13 +4796,13 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>46253</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>3860</v>
+        <v>4450</v>
       </c>
       <c r="C94" t="n">
-        <v>3860</v>
+        <v>4450</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3633,13 +4812,13 @@
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
-        <v>46254</v>
+        <v>46047</v>
       </c>
       <c r="B95" t="n">
-        <v>4050</v>
+        <v>4200</v>
       </c>
       <c r="C95" t="n">
-        <v>4050</v>
+        <v>4200</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3649,13 +4828,13 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>46255</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>3850</v>
+        <v>4070</v>
       </c>
       <c r="C96" t="n">
-        <v>3850</v>
+        <v>4070</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3665,13 +4844,13 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
-        <v>46256</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>4120</v>
+        <v>3970</v>
       </c>
       <c r="C97" t="n">
-        <v>4120</v>
+        <v>3970</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3681,13 +4860,13 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
-        <v>46257</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>4030</v>
+        <v>3925</v>
       </c>
       <c r="C98" t="n">
-        <v>4030</v>
+        <v>3925</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3697,13 +4876,13 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
-        <v>46258</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>3990</v>
+        <v>4190</v>
       </c>
       <c r="C99" t="n">
-        <v>3990</v>
+        <v>4190</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3713,13 +4892,13 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
-        <v>46259</v>
+        <v>46054</v>
       </c>
       <c r="B100" t="n">
-        <v>3880</v>
+        <v>3745</v>
       </c>
       <c r="C100" t="n">
-        <v>3880</v>
+        <v>3745</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3729,13 +4908,13 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
-        <v>46260</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>4100</v>
+        <v>3540</v>
       </c>
       <c r="C101" t="n">
-        <v>4100</v>
+        <v>3540</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3745,13 +4924,13 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
-        <v>46261</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>4020</v>
+        <v>3540</v>
       </c>
       <c r="C102" t="n">
-        <v>4020</v>
+        <v>3540</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3761,13 +4940,13 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
-        <v>46262</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>3600</v>
+        <v>3950</v>
       </c>
       <c r="C103" t="n">
-        <v>3600</v>
+        <v>3950</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3777,13 +4956,13 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
-        <v>46263</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>3820</v>
+        <v>3825</v>
       </c>
       <c r="C104" t="n">
-        <v>3820</v>
+        <v>3825</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3793,13 +4972,13 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
-        <v>46264</v>
+        <v>46061</v>
       </c>
       <c r="B105" t="n">
-        <v>3660</v>
+        <v>3825</v>
       </c>
       <c r="C105" t="n">
-        <v>3660</v>
+        <v>3825</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3809,13 +4988,13 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>46265</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>3730</v>
+        <v>3490</v>
       </c>
       <c r="C106" t="n">
-        <v>3730</v>
+        <v>3490</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,13 +5004,13 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
-        <v>46266</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>3845</v>
+        <v>3430</v>
       </c>
       <c r="C107" t="n">
-        <v>3845</v>
+        <v>3430</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3841,13 +5020,13 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
-        <v>46267</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>3975</v>
+        <v>3480</v>
       </c>
       <c r="C108" t="n">
-        <v>3975</v>
+        <v>3480</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3857,13 +5036,13 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>46270</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>3730</v>
+        <v>3620</v>
       </c>
       <c r="C109" t="n">
-        <v>3730</v>
+        <v>3620</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3873,13 +5052,13 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>46271</v>
+        <v>46068</v>
       </c>
       <c r="B110" t="n">
-        <v>3680</v>
+        <v>3570</v>
       </c>
       <c r="C110" t="n">
-        <v>3680</v>
+        <v>3570</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3889,13 +5068,13 @@
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
-        <v>46272</v>
+        <v>46069</v>
       </c>
       <c r="B111" t="n">
-        <v>3830</v>
+        <v>3520</v>
       </c>
       <c r="C111" t="n">
-        <v>3830</v>
+        <v>3520</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3905,13 +5084,13 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
-        <v>46273</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>3800</v>
+        <v>3405</v>
       </c>
       <c r="C112" t="n">
-        <v>3800</v>
+        <v>3405</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3921,13 +5100,13 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
-        <v>46274</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>3720</v>
+        <v>3515</v>
       </c>
       <c r="C113" t="n">
-        <v>3720</v>
+        <v>3515</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3937,13 +5116,13 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>3560</v>
+        <v>3680</v>
       </c>
       <c r="C114" t="n">
-        <v>3560</v>
+        <v>3680</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3953,13 +5132,13 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
-        <v>46276</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>3320</v>
+        <v>3660</v>
       </c>
       <c r="C115" t="n">
-        <v>3320</v>
+        <v>3660</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3969,13 +5148,13 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
-        <v>46277</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>3800</v>
+        <v>3790</v>
       </c>
       <c r="C116" t="n">
-        <v>3800</v>
+        <v>3790</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3985,13 +5164,13 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
-        <v>46278</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>3810</v>
+        <v>3920</v>
       </c>
       <c r="C117" t="n">
-        <v>3810</v>
+        <v>3920</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4001,13 +5180,13 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
-        <v>46279</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>3820</v>
+        <v>3760</v>
       </c>
       <c r="C118" t="n">
-        <v>3820</v>
+        <v>3760</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4017,13 +5196,13 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
-        <v>46280</v>
+        <v>46082</v>
       </c>
       <c r="B119" t="n">
-        <v>3830</v>
+        <v>4070</v>
       </c>
       <c r="C119" t="n">
-        <v>3830</v>
+        <v>4070</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4033,13 +5212,13 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
-        <v>46281</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>3900</v>
+        <v>4130</v>
       </c>
       <c r="C120" t="n">
-        <v>3900</v>
+        <v>4130</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4049,13 +5228,13 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
-        <v>46282</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>3730</v>
+        <v>4040</v>
       </c>
       <c r="C121" t="n">
-        <v>3730</v>
+        <v>4040</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4065,13 +5244,13 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
-        <v>46283</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>3210</v>
+        <v>3930</v>
       </c>
       <c r="C122" t="n">
-        <v>3210</v>
+        <v>3930</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4081,13 +5260,13 @@
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
-        <v>46284</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>3580</v>
+        <v>4000</v>
       </c>
       <c r="C123" t="n">
-        <v>3580</v>
+        <v>4000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4097,13 +5276,13 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
-        <v>46285</v>
+        <v>46089</v>
       </c>
       <c r="B124" t="n">
-        <v>3575</v>
+        <v>3890</v>
       </c>
       <c r="C124" t="n">
-        <v>3575</v>
+        <v>3890</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4113,13 +5292,13 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
-        <v>46286</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>3650</v>
+        <v>4030</v>
       </c>
       <c r="C125" t="n">
-        <v>3650</v>
+        <v>4030</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4129,13 +5308,13 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
-        <v>46287</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>3630</v>
+        <v>4005</v>
       </c>
       <c r="C126" t="n">
-        <v>3630</v>
+        <v>4005</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4145,13 +5324,13 @@
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
-        <v>46288</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>3590</v>
+        <v>3900</v>
       </c>
       <c r="C127" t="n">
-        <v>3590</v>
+        <v>3900</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4161,13 +5340,13 @@
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
-        <v>46289</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="C128" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4177,13 +5356,13 @@
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
-        <v>46290</v>
+        <v>46096</v>
       </c>
       <c r="B129" t="n">
-        <v>3100</v>
+        <v>3690</v>
       </c>
       <c r="C129" t="n">
-        <v>3100</v>
+        <v>3690</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4193,13 +5372,13 @@
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
-        <v>46291</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>3500</v>
+        <v>3840</v>
       </c>
       <c r="C130" t="n">
-        <v>3500</v>
+        <v>3840</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4209,13 +5388,13 @@
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
-        <v>46292</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>3440</v>
+        <v>3780</v>
       </c>
       <c r="C131" t="n">
-        <v>3440</v>
+        <v>3780</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4225,13 +5404,13 @@
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
-        <v>46293</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>3450</v>
+        <v>3580</v>
       </c>
       <c r="C132" t="n">
-        <v>3450</v>
+        <v>3580</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4241,13 +5420,13 @@
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
-        <v>46294</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>3400</v>
+        <v>3520</v>
       </c>
       <c r="C133" t="n">
-        <v>3400</v>
+        <v>3520</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4257,13 +5436,13 @@
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
-        <v>46295</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>3410</v>
+        <v>3470</v>
       </c>
       <c r="C134" t="n">
-        <v>3410</v>
+        <v>3470</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4273,13 +5452,13 @@
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
-        <v>46296</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>3230</v>
+        <v>3760</v>
       </c>
       <c r="C135" t="n">
-        <v>3230</v>
+        <v>3760</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4289,13 +5468,13 @@
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
-        <v>46297</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>2880</v>
+        <v>3800</v>
       </c>
       <c r="C136" t="n">
-        <v>2880</v>
+        <v>3800</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4305,13 +5484,13 @@
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
-        <v>46298</v>
+        <v>46110</v>
       </c>
       <c r="B137" t="n">
-        <v>3320</v>
+        <v>3700</v>
       </c>
       <c r="C137" t="n">
-        <v>3320</v>
+        <v>3700</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4321,13 +5500,13 @@
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
-        <v>46299</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>3330</v>
+        <v>3910</v>
       </c>
       <c r="C138" t="n">
-        <v>3330</v>
+        <v>3910</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4337,13 +5516,13 @@
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
-        <v>46300</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>3280</v>
+        <v>3860</v>
       </c>
       <c r="C139" t="n">
-        <v>3280</v>
+        <v>3860</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4353,13 +5532,13 @@
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
-        <v>46301</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>3270</v>
+        <v>3710</v>
       </c>
       <c r="C140" t="n">
-        <v>3270</v>
+        <v>3710</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4369,13 +5548,13 @@
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
-        <v>46302</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>3300</v>
+        <v>3760</v>
       </c>
       <c r="C141" t="n">
-        <v>3300</v>
+        <v>3760</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4385,15 +5564,2223 @@
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3605</v>
+      </c>
+      <c r="C142" t="n">
+        <v>3605</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3590</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3590</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3610</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3610</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3740</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3740</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3660</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3660</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B148" t="n">
+        <v>3560</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3560</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B149" t="n">
+        <v>3480</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3480</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3340</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3340</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B151" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3210</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3210</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B153" t="n">
+        <v>3230</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3230</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B154" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B155" t="n">
+        <v>3310</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3310</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B156" t="n">
+        <v>3280</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3280</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3170</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3170</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3255</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3255</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3190</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3190</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C160" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3180</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3180</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B162" t="n">
+        <v>3190</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3190</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B163" t="n">
+        <v>3270</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B164" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3380</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B165" t="n">
+        <v>3350</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3350</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3230</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3230</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3210</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3210</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3250</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B169" t="n">
+        <v>3270</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B170" t="n">
+        <v>3280</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3280</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B171" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B172" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3390</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3390</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B174" t="n">
+        <v>3350</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3350</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B175" t="n">
+        <v>3285</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3285</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B176" t="n">
+        <v>3220</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B177" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3030</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B179" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B180" t="n">
+        <v>3330</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3330</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B181" t="n">
+        <v>3330</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3330</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3380</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>3440</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>3425</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3425</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>3460</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3460</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>3510</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3510</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B187" t="n">
+        <v>3365</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3365</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B188" t="n">
+        <v>3425</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3425</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3435</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3435</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3550</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3550</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3470</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3470</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3590</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3590</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B193" t="n">
+        <v>3560</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3560</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B194" t="n">
+        <v>3450</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3450</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3490</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3490</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B196" t="n">
+        <v>3490</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3490</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B197" t="n">
+        <v>3585</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3585</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3630</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3630</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B199" t="n">
+        <v>3610</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3610</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B200" t="n">
+        <v>3630</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3630</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B201" t="n">
+        <v>3570</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3570</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3640</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3640</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B203" t="n">
+        <v>3630</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3630</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3610</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3610</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B205" t="n">
+        <v>3540</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3540</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B206" t="n">
+        <v>3570</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3570</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B207" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B208" t="n">
+        <v>3780</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3780</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B209" t="n">
+        <v>3780</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3780</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3740</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3740</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3880</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3880</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B212" t="n">
+        <v>3870</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3870</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3890</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3890</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B214" t="n">
+        <v>4020</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B215" t="n">
+        <v>3735</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3735</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B216" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B217" t="n">
+        <v>3770</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3770</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B218" t="n">
+        <v>3880</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3880</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4160</v>
+      </c>
+      <c r="C219" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B220" t="n">
+        <v>4290</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4290</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B221" t="n">
+        <v>4140</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4140</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B222" t="n">
+        <v>4220</v>
+      </c>
+      <c r="C222" t="n">
+        <v>4220</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B223" t="n">
+        <v>4180</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4180</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B224" t="n">
+        <v>3990</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B225" t="n">
+        <v>3970</v>
+      </c>
+      <c r="C225" t="n">
+        <v>3970</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4020</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4040</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4040</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4070</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4070</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B229" t="n">
+        <v>3930</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3930</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B230" t="n">
+        <v>3755</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3755</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B231" t="n">
+        <v>3740</v>
+      </c>
+      <c r="C231" t="n">
+        <v>3740</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B232" t="n">
+        <v>3860</v>
+      </c>
+      <c r="C232" t="n">
+        <v>3860</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B233" t="n">
+        <v>4050</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3850</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B235" t="n">
+        <v>4120</v>
+      </c>
+      <c r="C235" t="n">
+        <v>4120</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B236" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C236" t="n">
+        <v>4030</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B237" t="n">
+        <v>3990</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B238" t="n">
+        <v>3880</v>
+      </c>
+      <c r="C238" t="n">
+        <v>3880</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B239" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C239" t="n">
+        <v>4100</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B240" t="n">
+        <v>4020</v>
+      </c>
+      <c r="C240" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B241" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B242" t="n">
+        <v>3820</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3820</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3660</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3660</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B244" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3845</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3845</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B246" t="n">
+        <v>3975</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3975</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B248" t="n">
+        <v>3680</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3680</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B249" t="n">
+        <v>3830</v>
+      </c>
+      <c r="C249" t="n">
+        <v>3830</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B250" t="n">
+        <v>3800</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B251" t="n">
+        <v>3720</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3720</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3560</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3560</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3320</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3320</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3800</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3810</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3810</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B256" t="n">
+        <v>3820</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3820</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B257" t="n">
+        <v>3830</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3830</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B258" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B260" t="n">
+        <v>3210</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3210</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B261" t="n">
+        <v>3580</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3580</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3575</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3575</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3650</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3650</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3630</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3630</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3590</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3590</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B266" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B267" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B268" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B269" t="n">
+        <v>3440</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B270" t="n">
+        <v>3450</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3450</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B271" t="n">
+        <v>3400</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3410</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3410</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B273" t="n">
+        <v>3230</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3230</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B274" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C274" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B275" t="n">
+        <v>3320</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3320</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B276" t="n">
+        <v>3330</v>
+      </c>
+      <c r="C276" t="n">
+        <v>3330</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B277" t="n">
+        <v>3280</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3280</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B278" t="n">
+        <v>3270</v>
+      </c>
+      <c r="C278" t="n">
+        <v>3270</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B279" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C279" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="n">
         <v>46305</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B280" t="n">
         <v>3410</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C280" t="n">
         <v>3410</v>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -4410,7 +7797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4442,51 +7829,51 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46113</v>
+        <v>45901</v>
       </c>
       <c r="B2" t="n">
-        <v>3760</v>
+        <v>3560</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46143</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>3410</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
         <v>31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46174</v>
+        <v>45962</v>
       </c>
       <c r="B4" t="n">
-        <v>3630</v>
+        <v>3410</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>30</v>
@@ -4499,13 +7886,13 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46204</v>
+        <v>45992</v>
       </c>
       <c r="B5" t="n">
-        <v>4020</v>
+        <v>4210</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
         <v>31</v>
@@ -4518,13 +7905,13 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46235</v>
+        <v>46023</v>
       </c>
       <c r="B6" t="n">
-        <v>4290</v>
+        <v>4450</v>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
         <v>31</v>
@@ -4537,37 +7924,170 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46266</v>
+        <v>46054</v>
       </c>
       <c r="B7" t="n">
-        <v>3975</v>
+        <v>3950</v>
       </c>
       <c r="C7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
         <v>28</v>
       </c>
-      <c r="D7" t="n">
-        <v>30</v>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46296</v>
+        <v>46082</v>
       </c>
       <c r="B8" t="n">
-        <v>3410</v>
+        <v>4130</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>31</v>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3760</v>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3390</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3630</v>
+      </c>
+      <c r="C11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4020</v>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4290</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26</v>
+      </c>
+      <c r="D13" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3975</v>
+      </c>
+      <c r="C14" t="n">
+        <v>28</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3410</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>31</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4584,7 +8104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5113,6 +8633,519 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>46062</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>46053</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>46049</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>46032</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>46040</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>46031</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>46019</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>46022</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>46018</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>45988</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>45979</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>45970</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>45949</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>45957</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>45948</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>45939</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>45930</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>45927</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>45918</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/jordan_peak_load_daily.xlsx
+++ b/output/Data and Chart Outputs/jordan_peak_load_daily.xlsx
@@ -304,8 +304,9 @@
       <overlay val="0"/>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -315,21 +316,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
               <f>'Chart - Monthly maximum'!$A$2:$A$58</f>
@@ -340,11 +334,12 @@
               <f>'Chart - Monthly maximum'!$B$2:$B$58</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
+        <gapWidth val="30"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>

--- a/output/Data and Chart Outputs/jordan_peak_load_daily.xlsx
+++ b/output/Data and Chart Outputs/jordan_peak_load_daily.xlsx
@@ -195,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$C$2:$C$1787</f>
+              <f>'Chart'!$C$2:$C$1788</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$1787</f>
+              <f>'Chart'!$B$2:$B$1788</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1787"/>
+  <dimension ref="A1:C1788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15233,6 +15233,14 @@
         <v>46305</v>
       </c>
       <c r="B1787" t="n">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1788" t="n">
         <v>3410</v>
       </c>
     </row>
@@ -15734,7 +15742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1789"/>
+  <dimension ref="A1:E1790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44373,6 +44381,22 @@
       <c r="E1789" t="inlineStr">
         <is>
           <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1790" t="n">
+        <v>3410</v>
+      </c>
+      <c r="C1790" t="n">
+        <v>3410</v>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -46021,7 +46045,7 @@
         <v>3410</v>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
         <v>31</v>
@@ -46043,7 +46067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46080,35 +46104,35 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46305</v>
+        <v>46323</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>46313</v>
+        <v>46326</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>46307</v>
+        <v>46323</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>46304</v>
+        <v>46322</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46307</v>
+        <v>46323</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -46118,16 +46142,16 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46293</v>
+        <v>46305</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>46295</v>
+        <v>46313</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>46307</v>
+        <v>46323</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -46137,16 +46161,16 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46284</v>
+        <v>46296</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>46292</v>
+        <v>46304</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>46307</v>
+        <v>46323</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -46156,16 +46180,16 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46275</v>
+        <v>46293</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>46307</v>
+        <v>46323</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -46175,16 +46199,16 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46266</v>
+        <v>46284</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>46274</v>
+        <v>46292</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -46194,16 +46218,16 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46262</v>
+        <v>46275</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>46265</v>
+        <v>46283</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -46213,16 +46237,16 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46253</v>
+        <v>46266</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>46261</v>
+        <v>46274</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -46232,16 +46256,16 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>46252</v>
+        <v>46265</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -46251,16 +46275,16 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46235</v>
+        <v>46253</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>46243</v>
+        <v>46261</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -46270,16 +46294,16 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -46289,16 +46313,16 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46222</v>
+        <v>46235</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>46230</v>
+        <v>46243</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -46308,16 +46332,16 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46213</v>
+        <v>46231</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>46221</v>
+        <v>46234</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -46327,10 +46351,10 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46204</v>
+        <v>46222</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>46212</v>
+        <v>46230</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>46307</v>
@@ -46346,16 +46370,16 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46201</v>
+        <v>46213</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>46203</v>
+        <v>46221</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -46365,16 +46389,16 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46192</v>
+        <v>46204</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>46200</v>
+        <v>46212</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -46384,16 +46408,16 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46183</v>
+        <v>46201</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -46403,16 +46427,16 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46174</v>
+        <v>46192</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>46182</v>
+        <v>46200</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -46422,16 +46446,16 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>46173</v>
+        <v>46191</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -46441,16 +46465,16 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -46460,16 +46484,16 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46152</v>
+        <v>46170</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>46160</v>
+        <v>46173</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -46479,16 +46503,16 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46143</v>
+        <v>46161</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>46151</v>
+        <v>46169</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -46498,16 +46522,16 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46140</v>
+        <v>46152</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>46142</v>
+        <v>46160</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -46517,16 +46541,16 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46131</v>
+        <v>46143</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>46139</v>
+        <v>46151</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -46536,16 +46560,16 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46122</v>
+        <v>46140</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>46130</v>
+        <v>46142</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -46555,10 +46579,10 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46113</v>
+        <v>46131</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>46121</v>
+        <v>46139</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>46307</v>
@@ -46574,16 +46598,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46109</v>
+        <v>46122</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>46112</v>
+        <v>46130</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -46593,16 +46617,16 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46100</v>
+        <v>46113</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -46612,16 +46636,16 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46091</v>
+        <v>46109</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>46099</v>
+        <v>46112</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -46631,16 +46655,16 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46082</v>
+        <v>46100</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>46090</v>
+        <v>46108</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -46650,35 +46674,35 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46081</v>
+        <v>46091</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>46081</v>
+        <v>46099</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46072</v>
+        <v>46082</v>
       </c>
       <c r="B33" s="4" t="n">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -46688,35 +46712,35 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46063</v>
+        <v>46081</v>
       </c>
       <c r="B34" s="4" t="n">
-        <v>46071</v>
+        <v>46081</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46054</v>
+        <v>46072</v>
       </c>
       <c r="B35" s="4" t="n">
-        <v>46062</v>
+        <v>46080</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -46726,16 +46750,16 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="B36" s="4" t="n">
-        <v>46053</v>
+        <v>46071</v>
       </c>
       <c r="C36" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -46745,10 +46769,10 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46041</v>
+        <v>46054</v>
       </c>
       <c r="B37" s="4" t="n">
-        <v>46049</v>
+        <v>46062</v>
       </c>
       <c r="C37" s="4" t="n">
         <v>46307</v>
@@ -46764,16 +46788,16 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46032</v>
+        <v>46050</v>
       </c>
       <c r="B38" s="4" t="n">
-        <v>46040</v>
+        <v>46053</v>
       </c>
       <c r="C38" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -46783,16 +46807,16 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46023</v>
+        <v>46041</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>46031</v>
+        <v>46049</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -46802,16 +46826,16 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46019</v>
+        <v>46032</v>
       </c>
       <c r="B40" s="4" t="n">
-        <v>46022</v>
+        <v>46040</v>
       </c>
       <c r="C40" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -46821,16 +46845,16 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46010</v>
+        <v>46023</v>
       </c>
       <c r="B41" s="4" t="n">
-        <v>46018</v>
+        <v>46031</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -46840,16 +46864,16 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46001</v>
+        <v>46019</v>
       </c>
       <c r="B42" s="4" t="n">
-        <v>46009</v>
+        <v>46022</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -46859,16 +46883,16 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>45992</v>
+        <v>46010</v>
       </c>
       <c r="B43" s="4" t="n">
-        <v>46000</v>
+        <v>46018</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -46878,16 +46902,16 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="B44" s="4" t="n">
-        <v>45991</v>
+        <v>46009</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -46897,10 +46921,10 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>45980</v>
+        <v>45992</v>
       </c>
       <c r="B45" s="4" t="n">
-        <v>45988</v>
+        <v>46000</v>
       </c>
       <c r="C45" s="4" t="n">
         <v>46307</v>
@@ -46916,16 +46940,16 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>45971</v>
+        <v>45989</v>
       </c>
       <c r="B46" s="4" t="n">
-        <v>45979</v>
+        <v>45991</v>
       </c>
       <c r="C46" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -46935,16 +46959,16 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>45962</v>
+        <v>45980</v>
       </c>
       <c r="B47" s="4" t="n">
-        <v>45970</v>
+        <v>45988</v>
       </c>
       <c r="C47" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -46954,16 +46978,16 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>45958</v>
+        <v>45971</v>
       </c>
       <c r="B48" s="4" t="n">
-        <v>45961</v>
+        <v>45979</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -46973,16 +46997,16 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>45949</v>
+        <v>45962</v>
       </c>
       <c r="B49" s="4" t="n">
-        <v>45957</v>
+        <v>45970</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -46992,16 +47016,16 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>45940</v>
+        <v>45958</v>
       </c>
       <c r="B50" s="4" t="n">
-        <v>45948</v>
+        <v>45961</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -47011,10 +47035,10 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>45931</v>
+        <v>45949</v>
       </c>
       <c r="B51" s="4" t="n">
-        <v>45939</v>
+        <v>45957</v>
       </c>
       <c r="C51" s="4" t="n">
         <v>46307</v>
@@ -47030,16 +47054,16 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>45928</v>
+        <v>45940</v>
       </c>
       <c r="B52" s="4" t="n">
-        <v>45930</v>
+        <v>45948</v>
       </c>
       <c r="C52" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -47049,16 +47073,16 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="B53" s="4" t="n">
-        <v>45927</v>
+        <v>45939</v>
       </c>
       <c r="C53" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -47068,16 +47092,16 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>45910</v>
+        <v>45928</v>
       </c>
       <c r="B54" s="4" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="C54" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -47087,16 +47111,16 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>45901</v>
+        <v>45919</v>
       </c>
       <c r="B55" s="4" t="n">
-        <v>45909</v>
+        <v>45927</v>
       </c>
       <c r="C55" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -47106,16 +47130,16 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>45897</v>
+        <v>45910</v>
       </c>
       <c r="B56" s="4" t="n">
-        <v>45900</v>
+        <v>45918</v>
       </c>
       <c r="C56" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -47125,10 +47149,10 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>45888</v>
+        <v>45901</v>
       </c>
       <c r="B57" s="4" t="n">
-        <v>45896</v>
+        <v>45909</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>46307</v>
@@ -47144,16 +47168,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>45879</v>
+        <v>45897</v>
       </c>
       <c r="B58" s="4" t="n">
-        <v>45887</v>
+        <v>45900</v>
       </c>
       <c r="C58" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -47163,16 +47187,16 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>45870</v>
+        <v>45888</v>
       </c>
       <c r="B59" s="4" t="n">
-        <v>45878</v>
+        <v>45896</v>
       </c>
       <c r="C59" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -47182,16 +47206,16 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>45866</v>
+        <v>45879</v>
       </c>
       <c r="B60" s="4" t="n">
-        <v>45869</v>
+        <v>45887</v>
       </c>
       <c r="C60" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -47201,16 +47225,16 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>45857</v>
+        <v>45870</v>
       </c>
       <c r="B61" s="4" t="n">
-        <v>45865</v>
+        <v>45878</v>
       </c>
       <c r="C61" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -47220,16 +47244,16 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>45848</v>
+        <v>45866</v>
       </c>
       <c r="B62" s="4" t="n">
-        <v>45856</v>
+        <v>45869</v>
       </c>
       <c r="C62" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -47239,16 +47263,16 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>45839</v>
+        <v>45857</v>
       </c>
       <c r="B63" s="4" t="n">
-        <v>45847</v>
+        <v>45865</v>
       </c>
       <c r="C63" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -47258,16 +47282,16 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>45836</v>
+        <v>45848</v>
       </c>
       <c r="B64" s="4" t="n">
-        <v>45838</v>
+        <v>45856</v>
       </c>
       <c r="C64" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -47277,16 +47301,16 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
-        <v>45827</v>
+        <v>45839</v>
       </c>
       <c r="B65" s="4" t="n">
-        <v>45835</v>
+        <v>45847</v>
       </c>
       <c r="C65" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -47296,16 +47320,16 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>45818</v>
+        <v>45836</v>
       </c>
       <c r="B66" s="4" t="n">
-        <v>45826</v>
+        <v>45838</v>
       </c>
       <c r="C66" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -47315,16 +47339,16 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>45809</v>
+        <v>45827</v>
       </c>
       <c r="B67" s="4" t="n">
-        <v>45817</v>
+        <v>45835</v>
       </c>
       <c r="C67" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -47334,16 +47358,16 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>45805</v>
+        <v>45818</v>
       </c>
       <c r="B68" s="4" t="n">
-        <v>45808</v>
+        <v>45826</v>
       </c>
       <c r="C68" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -47353,16 +47377,16 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>45796</v>
+        <v>45809</v>
       </c>
       <c r="B69" s="4" t="n">
-        <v>45804</v>
+        <v>45817</v>
       </c>
       <c r="C69" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -47372,16 +47396,16 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>45787</v>
+        <v>45805</v>
       </c>
       <c r="B70" s="4" t="n">
-        <v>45795</v>
+        <v>45808</v>
       </c>
       <c r="C70" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -47391,16 +47415,16 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>45778</v>
+        <v>45796</v>
       </c>
       <c r="B71" s="4" t="n">
-        <v>45786</v>
+        <v>45804</v>
       </c>
       <c r="C71" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -47410,16 +47434,16 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
-        <v>45775</v>
+        <v>45787</v>
       </c>
       <c r="B72" s="4" t="n">
-        <v>45777</v>
+        <v>45795</v>
       </c>
       <c r="C72" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -47429,16 +47453,16 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>45766</v>
+        <v>45778</v>
       </c>
       <c r="B73" s="4" t="n">
-        <v>45774</v>
+        <v>45786</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -47448,16 +47472,16 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>45757</v>
+        <v>45775</v>
       </c>
       <c r="B74" s="4" t="n">
-        <v>45765</v>
+        <v>45777</v>
       </c>
       <c r="C74" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -47467,16 +47491,16 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>45748</v>
+        <v>45766</v>
       </c>
       <c r="B75" s="4" t="n">
-        <v>45756</v>
+        <v>45774</v>
       </c>
       <c r="C75" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -47486,35 +47510,35 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>45744</v>
+        <v>45757</v>
       </c>
       <c r="B76" s="4" t="n">
-        <v>45747</v>
+        <v>45765</v>
       </c>
       <c r="C76" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>45735</v>
+        <v>45748</v>
       </c>
       <c r="B77" s="4" t="n">
-        <v>45743</v>
+        <v>45756</v>
       </c>
       <c r="C77" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -47524,35 +47548,35 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>45726</v>
+        <v>45744</v>
       </c>
       <c r="B78" s="4" t="n">
-        <v>45734</v>
+        <v>45747</v>
       </c>
       <c r="C78" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>45717</v>
+        <v>45735</v>
       </c>
       <c r="B79" s="4" t="n">
-        <v>45725</v>
+        <v>45743</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -47562,35 +47586,35 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>45716</v>
+        <v>45726</v>
       </c>
       <c r="B80" s="4" t="n">
-        <v>45716</v>
+        <v>45734</v>
       </c>
       <c r="C80" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>45707</v>
+        <v>45717</v>
       </c>
       <c r="B81" s="4" t="n">
-        <v>45715</v>
+        <v>45725</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -47600,35 +47624,35 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>45698</v>
+        <v>45716</v>
       </c>
       <c r="B82" s="4" t="n">
-        <v>45706</v>
+        <v>45716</v>
       </c>
       <c r="C82" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>45689</v>
+        <v>45707</v>
       </c>
       <c r="B83" s="4" t="n">
-        <v>45697</v>
+        <v>45715</v>
       </c>
       <c r="C83" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -47638,16 +47662,16 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>45685</v>
+        <v>45698</v>
       </c>
       <c r="B84" s="4" t="n">
-        <v>45688</v>
+        <v>45706</v>
       </c>
       <c r="C84" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -47657,16 +47681,16 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>45676</v>
+        <v>45689</v>
       </c>
       <c r="B85" s="4" t="n">
-        <v>45684</v>
+        <v>45697</v>
       </c>
       <c r="C85" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -47676,16 +47700,16 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>45667</v>
+        <v>45685</v>
       </c>
       <c r="B86" s="4" t="n">
-        <v>45675</v>
+        <v>45688</v>
       </c>
       <c r="C86" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -47695,16 +47719,16 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>45658</v>
+        <v>45676</v>
       </c>
       <c r="B87" s="4" t="n">
-        <v>45666</v>
+        <v>45684</v>
       </c>
       <c r="C87" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -47714,16 +47738,16 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>45654</v>
+        <v>45667</v>
       </c>
       <c r="B88" s="4" t="n">
-        <v>45657</v>
+        <v>45675</v>
       </c>
       <c r="C88" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -47733,16 +47757,16 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>45645</v>
+        <v>45658</v>
       </c>
       <c r="B89" s="4" t="n">
-        <v>45653</v>
+        <v>45666</v>
       </c>
       <c r="C89" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -47752,16 +47776,16 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>45636</v>
+        <v>45654</v>
       </c>
       <c r="B90" s="4" t="n">
-        <v>45644</v>
+        <v>45657</v>
       </c>
       <c r="C90" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -47771,16 +47795,16 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
-        <v>45627</v>
+        <v>45645</v>
       </c>
       <c r="B91" s="4" t="n">
-        <v>45635</v>
+        <v>45653</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -47790,16 +47814,16 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>45624</v>
+        <v>45636</v>
       </c>
       <c r="B92" s="4" t="n">
-        <v>45626</v>
+        <v>45644</v>
       </c>
       <c r="C92" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -47809,16 +47833,16 @@
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
-        <v>45615</v>
+        <v>45627</v>
       </c>
       <c r="B93" s="4" t="n">
-        <v>45623</v>
+        <v>45635</v>
       </c>
       <c r="C93" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -47828,16 +47852,16 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>45606</v>
+        <v>45624</v>
       </c>
       <c r="B94" s="4" t="n">
-        <v>45614</v>
+        <v>45626</v>
       </c>
       <c r="C94" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -47847,35 +47871,35 @@
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
-        <v>45597</v>
+        <v>45615</v>
       </c>
       <c r="B95" s="4" t="n">
-        <v>45605</v>
+        <v>45623</v>
       </c>
       <c r="C95" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>45593</v>
+        <v>45606</v>
       </c>
       <c r="B96" s="4" t="n">
-        <v>45596</v>
+        <v>45614</v>
       </c>
       <c r="C96" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -47885,35 +47909,35 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
-        <v>45584</v>
+        <v>45597</v>
       </c>
       <c r="B97" s="4" t="n">
-        <v>45592</v>
+        <v>45605</v>
       </c>
       <c r="C97" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
-        <v>45575</v>
+        <v>45593</v>
       </c>
       <c r="B98" s="4" t="n">
-        <v>45583</v>
+        <v>45596</v>
       </c>
       <c r="C98" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -47923,16 +47947,16 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
-        <v>45566</v>
+        <v>45584</v>
       </c>
       <c r="B99" s="4" t="n">
-        <v>45574</v>
+        <v>45592</v>
       </c>
       <c r="C99" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -47942,16 +47966,16 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
-        <v>45563</v>
+        <v>45575</v>
       </c>
       <c r="B100" s="4" t="n">
-        <v>45565</v>
+        <v>45583</v>
       </c>
       <c r="C100" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -47961,16 +47985,16 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
-        <v>45554</v>
+        <v>45566</v>
       </c>
       <c r="B101" s="4" t="n">
-        <v>45562</v>
+        <v>45574</v>
       </c>
       <c r="C101" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -47980,16 +48004,16 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
-        <v>45545</v>
+        <v>45563</v>
       </c>
       <c r="B102" s="4" t="n">
-        <v>45553</v>
+        <v>45565</v>
       </c>
       <c r="C102" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -47999,16 +48023,16 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
-        <v>45536</v>
+        <v>45554</v>
       </c>
       <c r="B103" s="4" t="n">
-        <v>45544</v>
+        <v>45562</v>
       </c>
       <c r="C103" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -48018,16 +48042,16 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
-        <v>45532</v>
+        <v>45545</v>
       </c>
       <c r="B104" s="4" t="n">
-        <v>45535</v>
+        <v>45553</v>
       </c>
       <c r="C104" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -48037,10 +48061,10 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
-        <v>45523</v>
+        <v>45536</v>
       </c>
       <c r="B105" s="4" t="n">
-        <v>45531</v>
+        <v>45544</v>
       </c>
       <c r="C105" s="4" t="n">
         <v>46307</v>
@@ -48056,16 +48080,16 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>45514</v>
+        <v>45532</v>
       </c>
       <c r="B106" s="4" t="n">
-        <v>45522</v>
+        <v>45535</v>
       </c>
       <c r="C106" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -48075,16 +48099,16 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
-        <v>45505</v>
+        <v>45523</v>
       </c>
       <c r="B107" s="4" t="n">
-        <v>45513</v>
+        <v>45531</v>
       </c>
       <c r="C107" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -48094,16 +48118,16 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
-        <v>45501</v>
+        <v>45514</v>
       </c>
       <c r="B108" s="4" t="n">
-        <v>45504</v>
+        <v>45522</v>
       </c>
       <c r="C108" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -48113,16 +48137,16 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>45492</v>
+        <v>45505</v>
       </c>
       <c r="B109" s="4" t="n">
-        <v>45500</v>
+        <v>45513</v>
       </c>
       <c r="C109" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -48132,16 +48156,16 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>45483</v>
+        <v>45501</v>
       </c>
       <c r="B110" s="4" t="n">
-        <v>45491</v>
+        <v>45504</v>
       </c>
       <c r="C110" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -48151,16 +48175,16 @@
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
-        <v>45474</v>
+        <v>45492</v>
       </c>
       <c r="B111" s="4" t="n">
-        <v>45482</v>
+        <v>45500</v>
       </c>
       <c r="C111" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -48170,16 +48194,16 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
-        <v>45471</v>
+        <v>45483</v>
       </c>
       <c r="B112" s="4" t="n">
-        <v>45473</v>
+        <v>45491</v>
       </c>
       <c r="C112" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -48189,16 +48213,16 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
-        <v>45462</v>
+        <v>45474</v>
       </c>
       <c r="B113" s="4" t="n">
-        <v>45470</v>
+        <v>45482</v>
       </c>
       <c r="C113" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -48208,16 +48232,16 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
-        <v>45453</v>
+        <v>45471</v>
       </c>
       <c r="B114" s="4" t="n">
-        <v>45461</v>
+        <v>45473</v>
       </c>
       <c r="C114" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -48227,16 +48251,16 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
-        <v>45444</v>
+        <v>45462</v>
       </c>
       <c r="B115" s="4" t="n">
-        <v>45452</v>
+        <v>45470</v>
       </c>
       <c r="C115" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -48246,16 +48270,16 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
-        <v>45440</v>
+        <v>45453</v>
       </c>
       <c r="B116" s="4" t="n">
-        <v>45443</v>
+        <v>45461</v>
       </c>
       <c r="C116" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -48265,16 +48289,16 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
-        <v>45431</v>
+        <v>45444</v>
       </c>
       <c r="B117" s="4" t="n">
-        <v>45439</v>
+        <v>45452</v>
       </c>
       <c r="C117" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D117" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -48284,16 +48308,16 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
-        <v>45422</v>
+        <v>45440</v>
       </c>
       <c r="B118" s="4" t="n">
-        <v>45430</v>
+        <v>45443</v>
       </c>
       <c r="C118" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -48303,16 +48327,16 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
-        <v>45413</v>
+        <v>45431</v>
       </c>
       <c r="B119" s="4" t="n">
-        <v>45421</v>
+        <v>45439</v>
       </c>
       <c r="C119" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -48322,16 +48346,16 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
-        <v>45410</v>
+        <v>45422</v>
       </c>
       <c r="B120" s="4" t="n">
-        <v>45412</v>
+        <v>45430</v>
       </c>
       <c r="C120" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -48341,10 +48365,10 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
-        <v>45401</v>
+        <v>45413</v>
       </c>
       <c r="B121" s="4" t="n">
-        <v>45409</v>
+        <v>45421</v>
       </c>
       <c r="C121" s="4" t="n">
         <v>46307</v>
@@ -48360,16 +48384,16 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
-        <v>45392</v>
+        <v>45410</v>
       </c>
       <c r="B122" s="4" t="n">
-        <v>45400</v>
+        <v>45412</v>
       </c>
       <c r="C122" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -48379,16 +48403,16 @@
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
-        <v>45383</v>
+        <v>45401</v>
       </c>
       <c r="B123" s="4" t="n">
-        <v>45391</v>
+        <v>45409</v>
       </c>
       <c r="C123" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -48398,16 +48422,16 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
-        <v>45379</v>
+        <v>45392</v>
       </c>
       <c r="B124" s="4" t="n">
-        <v>45382</v>
+        <v>45400</v>
       </c>
       <c r="C124" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -48417,16 +48441,16 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
-        <v>45370</v>
+        <v>45383</v>
       </c>
       <c r="B125" s="4" t="n">
-        <v>45378</v>
+        <v>45391</v>
       </c>
       <c r="C125" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -48436,16 +48460,16 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
-        <v>45361</v>
+        <v>45379</v>
       </c>
       <c r="B126" s="4" t="n">
-        <v>45369</v>
+        <v>45382</v>
       </c>
       <c r="C126" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D126" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -48455,16 +48479,16 @@
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
-        <v>45352</v>
+        <v>45370</v>
       </c>
       <c r="B127" s="4" t="n">
-        <v>45360</v>
+        <v>45378</v>
       </c>
       <c r="C127" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D127" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -48474,16 +48498,16 @@
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
-        <v>45350</v>
+        <v>45361</v>
       </c>
       <c r="B128" s="4" t="n">
-        <v>45351</v>
+        <v>45369</v>
       </c>
       <c r="C128" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -48493,16 +48517,16 @@
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
-        <v>45341</v>
+        <v>45352</v>
       </c>
       <c r="B129" s="4" t="n">
-        <v>45349</v>
+        <v>45360</v>
       </c>
       <c r="C129" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D129" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -48512,16 +48536,16 @@
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
-        <v>45332</v>
+        <v>45350</v>
       </c>
       <c r="B130" s="4" t="n">
-        <v>45340</v>
+        <v>45351</v>
       </c>
       <c r="C130" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -48531,16 +48555,16 @@
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
-        <v>45323</v>
+        <v>45341</v>
       </c>
       <c r="B131" s="4" t="n">
-        <v>45331</v>
+        <v>45349</v>
       </c>
       <c r="C131" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -48550,16 +48574,16 @@
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
-        <v>45319</v>
+        <v>45332</v>
       </c>
       <c r="B132" s="4" t="n">
-        <v>45322</v>
+        <v>45340</v>
       </c>
       <c r="C132" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -48569,16 +48593,16 @@
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
-        <v>45310</v>
+        <v>45323</v>
       </c>
       <c r="B133" s="4" t="n">
-        <v>45318</v>
+        <v>45331</v>
       </c>
       <c r="C133" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -48588,16 +48612,16 @@
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
-        <v>45301</v>
+        <v>45319</v>
       </c>
       <c r="B134" s="4" t="n">
-        <v>45309</v>
+        <v>45322</v>
       </c>
       <c r="C134" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D134" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -48607,16 +48631,16 @@
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
-        <v>45292</v>
+        <v>45310</v>
       </c>
       <c r="B135" s="4" t="n">
-        <v>45300</v>
+        <v>45318</v>
       </c>
       <c r="C135" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -48626,16 +48650,16 @@
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
-        <v>45288</v>
+        <v>45301</v>
       </c>
       <c r="B136" s="4" t="n">
-        <v>45291</v>
+        <v>45309</v>
       </c>
       <c r="C136" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -48645,10 +48669,10 @@
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
-        <v>45279</v>
+        <v>45292</v>
       </c>
       <c r="B137" s="4" t="n">
-        <v>45287</v>
+        <v>45300</v>
       </c>
       <c r="C137" s="4" t="n">
         <v>46307</v>
@@ -48664,16 +48688,16 @@
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
-        <v>45270</v>
+        <v>45288</v>
       </c>
       <c r="B138" s="4" t="n">
-        <v>45278</v>
+        <v>45291</v>
       </c>
       <c r="C138" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -48683,16 +48707,16 @@
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
-        <v>45261</v>
+        <v>45279</v>
       </c>
       <c r="B139" s="4" t="n">
-        <v>45269</v>
+        <v>45287</v>
       </c>
       <c r="C139" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -48702,16 +48726,16 @@
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
-        <v>45258</v>
+        <v>45270</v>
       </c>
       <c r="B140" s="4" t="n">
-        <v>45260</v>
+        <v>45278</v>
       </c>
       <c r="C140" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -48721,16 +48745,16 @@
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
-        <v>45249</v>
+        <v>45261</v>
       </c>
       <c r="B141" s="4" t="n">
-        <v>45257</v>
+        <v>45269</v>
       </c>
       <c r="C141" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D141" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -48740,16 +48764,16 @@
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
-        <v>45240</v>
+        <v>45258</v>
       </c>
       <c r="B142" s="4" t="n">
-        <v>45248</v>
+        <v>45260</v>
       </c>
       <c r="C142" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -48759,10 +48783,10 @@
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
-        <v>45231</v>
+        <v>45249</v>
       </c>
       <c r="B143" s="4" t="n">
-        <v>45239</v>
+        <v>45257</v>
       </c>
       <c r="C143" s="4" t="n">
         <v>46307</v>
@@ -48778,16 +48802,16 @@
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
-        <v>45227</v>
+        <v>45240</v>
       </c>
       <c r="B144" s="4" t="n">
-        <v>45230</v>
+        <v>45248</v>
       </c>
       <c r="C144" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -48797,16 +48821,16 @@
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
-        <v>45218</v>
+        <v>45231</v>
       </c>
       <c r="B145" s="4" t="n">
-        <v>45226</v>
+        <v>45239</v>
       </c>
       <c r="C145" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -48816,16 +48840,16 @@
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
-        <v>45209</v>
+        <v>45227</v>
       </c>
       <c r="B146" s="4" t="n">
-        <v>45217</v>
+        <v>45230</v>
       </c>
       <c r="C146" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D146" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -48835,16 +48859,16 @@
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
-        <v>45200</v>
+        <v>45218</v>
       </c>
       <c r="B147" s="4" t="n">
-        <v>45208</v>
+        <v>45226</v>
       </c>
       <c r="C147" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -48854,16 +48878,16 @@
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
-        <v>45197</v>
+        <v>45209</v>
       </c>
       <c r="B148" s="4" t="n">
-        <v>45199</v>
+        <v>45217</v>
       </c>
       <c r="C148" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -48873,16 +48897,16 @@
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
-        <v>45188</v>
+        <v>45200</v>
       </c>
       <c r="B149" s="4" t="n">
-        <v>45196</v>
+        <v>45208</v>
       </c>
       <c r="C149" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -48892,16 +48916,16 @@
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
-        <v>45179</v>
+        <v>45197</v>
       </c>
       <c r="B150" s="4" t="n">
-        <v>45187</v>
+        <v>45199</v>
       </c>
       <c r="C150" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D150" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -48911,10 +48935,10 @@
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
-        <v>45170</v>
+        <v>45188</v>
       </c>
       <c r="B151" s="4" t="n">
-        <v>45178</v>
+        <v>45196</v>
       </c>
       <c r="C151" s="4" t="n">
         <v>46307</v>
@@ -48930,16 +48954,16 @@
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
-        <v>45166</v>
+        <v>45179</v>
       </c>
       <c r="B152" s="4" t="n">
-        <v>45169</v>
+        <v>45187</v>
       </c>
       <c r="C152" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D152" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -48949,16 +48973,16 @@
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
-        <v>45157</v>
+        <v>45170</v>
       </c>
       <c r="B153" s="4" t="n">
-        <v>45165</v>
+        <v>45178</v>
       </c>
       <c r="C153" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -48968,16 +48992,16 @@
     </row>
     <row r="154">
       <c r="A154" s="4" t="n">
-        <v>45148</v>
+        <v>45166</v>
       </c>
       <c r="B154" s="4" t="n">
-        <v>45156</v>
+        <v>45169</v>
       </c>
       <c r="C154" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D154" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -48987,16 +49011,16 @@
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
-        <v>45139</v>
+        <v>45157</v>
       </c>
       <c r="B155" s="4" t="n">
-        <v>45147</v>
+        <v>45165</v>
       </c>
       <c r="C155" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D155" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -49006,16 +49030,16 @@
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
-        <v>45135</v>
+        <v>45148</v>
       </c>
       <c r="B156" s="4" t="n">
-        <v>45138</v>
+        <v>45156</v>
       </c>
       <c r="C156" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -49025,16 +49049,16 @@
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
-        <v>45126</v>
+        <v>45139</v>
       </c>
       <c r="B157" s="4" t="n">
-        <v>45134</v>
+        <v>45147</v>
       </c>
       <c r="C157" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -49044,16 +49068,16 @@
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
-        <v>45117</v>
+        <v>45135</v>
       </c>
       <c r="B158" s="4" t="n">
-        <v>45125</v>
+        <v>45138</v>
       </c>
       <c r="C158" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D158" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -49063,10 +49087,10 @@
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
-        <v>45108</v>
+        <v>45126</v>
       </c>
       <c r="B159" s="4" t="n">
-        <v>45116</v>
+        <v>45134</v>
       </c>
       <c r="C159" s="4" t="n">
         <v>46307</v>
@@ -49082,29 +49106,29 @@
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
-        <v>45105</v>
+        <v>45117</v>
       </c>
       <c r="B160" s="4" t="n">
-        <v>45107</v>
+        <v>45125</v>
       </c>
       <c r="C160" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
-        <v>45096</v>
+        <v>45108</v>
       </c>
       <c r="B161" s="4" t="n">
-        <v>45104</v>
+        <v>45116</v>
       </c>
       <c r="C161" s="4" t="n">
         <v>46307</v>
@@ -49120,35 +49144,35 @@
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
-        <v>45087</v>
+        <v>45105</v>
       </c>
       <c r="B162" s="4" t="n">
-        <v>45095</v>
+        <v>45107</v>
       </c>
       <c r="C162" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D162" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
-        <v>45078</v>
+        <v>45096</v>
       </c>
       <c r="B163" s="4" t="n">
-        <v>45086</v>
+        <v>45104</v>
       </c>
       <c r="C163" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -49158,16 +49182,16 @@
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
-        <v>45074</v>
+        <v>45087</v>
       </c>
       <c r="B164" s="4" t="n">
-        <v>45077</v>
+        <v>45095</v>
       </c>
       <c r="C164" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -49177,16 +49201,16 @@
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
-        <v>45065</v>
+        <v>45078</v>
       </c>
       <c r="B165" s="4" t="n">
-        <v>45073</v>
+        <v>45086</v>
       </c>
       <c r="C165" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -49196,16 +49220,16 @@
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
-        <v>45056</v>
+        <v>45074</v>
       </c>
       <c r="B166" s="4" t="n">
-        <v>45064</v>
+        <v>45077</v>
       </c>
       <c r="C166" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D166" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -49215,16 +49239,16 @@
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
-        <v>45047</v>
+        <v>45065</v>
       </c>
       <c r="B167" s="4" t="n">
-        <v>45055</v>
+        <v>45073</v>
       </c>
       <c r="C167" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D167" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -49234,35 +49258,35 @@
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
-        <v>45044</v>
+        <v>45056</v>
       </c>
       <c r="B168" s="4" t="n">
-        <v>45046</v>
+        <v>45064</v>
       </c>
       <c r="C168" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
-        <v>45035</v>
+        <v>45047</v>
       </c>
       <c r="B169" s="4" t="n">
-        <v>45043</v>
+        <v>45055</v>
       </c>
       <c r="C169" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D169" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -49272,35 +49296,35 @@
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
-        <v>45026</v>
+        <v>45044</v>
       </c>
       <c r="B170" s="4" t="n">
-        <v>45034</v>
+        <v>45046</v>
       </c>
       <c r="C170" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D170" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
-        <v>45017</v>
+        <v>45035</v>
       </c>
       <c r="B171" s="4" t="n">
-        <v>45025</v>
+        <v>45043</v>
       </c>
       <c r="C171" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -49310,16 +49334,16 @@
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
-        <v>45013</v>
+        <v>45026</v>
       </c>
       <c r="B172" s="4" t="n">
-        <v>45016</v>
+        <v>45034</v>
       </c>
       <c r="C172" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -49329,16 +49353,16 @@
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
-        <v>45004</v>
+        <v>45017</v>
       </c>
       <c r="B173" s="4" t="n">
-        <v>45012</v>
+        <v>45025</v>
       </c>
       <c r="C173" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D173" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -49348,16 +49372,16 @@
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
-        <v>44995</v>
+        <v>45013</v>
       </c>
       <c r="B174" s="4" t="n">
-        <v>45003</v>
+        <v>45016</v>
       </c>
       <c r="C174" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D174" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -49367,10 +49391,10 @@
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
-        <v>44986</v>
+        <v>45004</v>
       </c>
       <c r="B175" s="4" t="n">
-        <v>44994</v>
+        <v>45012</v>
       </c>
       <c r="C175" s="4" t="n">
         <v>46307</v>
@@ -49386,16 +49410,16 @@
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
-        <v>44985</v>
+        <v>44995</v>
       </c>
       <c r="B176" s="4" t="n">
-        <v>44985</v>
+        <v>45003</v>
       </c>
       <c r="C176" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -49405,10 +49429,10 @@
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
-        <v>44976</v>
+        <v>44986</v>
       </c>
       <c r="B177" s="4" t="n">
-        <v>44984</v>
+        <v>44994</v>
       </c>
       <c r="C177" s="4" t="n">
         <v>46307</v>
@@ -49424,16 +49448,16 @@
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
-        <v>44967</v>
+        <v>44985</v>
       </c>
       <c r="B178" s="4" t="n">
-        <v>44975</v>
+        <v>44985</v>
       </c>
       <c r="C178" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -49443,16 +49467,16 @@
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
-        <v>44958</v>
+        <v>44976</v>
       </c>
       <c r="B179" s="4" t="n">
-        <v>44966</v>
+        <v>44984</v>
       </c>
       <c r="C179" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D179" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -49462,16 +49486,16 @@
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
-        <v>44954</v>
+        <v>44967</v>
       </c>
       <c r="B180" s="4" t="n">
-        <v>44957</v>
+        <v>44975</v>
       </c>
       <c r="C180" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -49481,16 +49505,16 @@
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
-        <v>44945</v>
+        <v>44958</v>
       </c>
       <c r="B181" s="4" t="n">
-        <v>44953</v>
+        <v>44966</v>
       </c>
       <c r="C181" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D181" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -49500,16 +49524,16 @@
     </row>
     <row r="182">
       <c r="A182" s="4" t="n">
-        <v>44936</v>
+        <v>44954</v>
       </c>
       <c r="B182" s="4" t="n">
-        <v>44944</v>
+        <v>44957</v>
       </c>
       <c r="C182" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D182" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -49519,16 +49543,16 @@
     </row>
     <row r="183">
       <c r="A183" s="4" t="n">
-        <v>44927</v>
+        <v>44945</v>
       </c>
       <c r="B183" s="4" t="n">
-        <v>44935</v>
+        <v>44953</v>
       </c>
       <c r="C183" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D183" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -49538,16 +49562,16 @@
     </row>
     <row r="184">
       <c r="A184" s="4" t="n">
-        <v>44923</v>
+        <v>44936</v>
       </c>
       <c r="B184" s="4" t="n">
-        <v>44926</v>
+        <v>44944</v>
       </c>
       <c r="C184" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -49557,16 +49581,16 @@
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
-        <v>44914</v>
+        <v>44927</v>
       </c>
       <c r="B185" s="4" t="n">
-        <v>44922</v>
+        <v>44935</v>
       </c>
       <c r="C185" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D185" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -49576,16 +49600,16 @@
     </row>
     <row r="186">
       <c r="A186" s="4" t="n">
-        <v>44905</v>
+        <v>44923</v>
       </c>
       <c r="B186" s="4" t="n">
-        <v>44913</v>
+        <v>44926</v>
       </c>
       <c r="C186" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D186" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -49595,16 +49619,16 @@
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
-        <v>44896</v>
+        <v>44914</v>
       </c>
       <c r="B187" s="4" t="n">
-        <v>44904</v>
+        <v>44922</v>
       </c>
       <c r="C187" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -49614,16 +49638,16 @@
     </row>
     <row r="188">
       <c r="A188" s="4" t="n">
-        <v>44893</v>
+        <v>44905</v>
       </c>
       <c r="B188" s="4" t="n">
-        <v>44895</v>
+        <v>44913</v>
       </c>
       <c r="C188" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -49633,10 +49657,10 @@
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
-        <v>44884</v>
+        <v>44896</v>
       </c>
       <c r="B189" s="4" t="n">
-        <v>44892</v>
+        <v>44904</v>
       </c>
       <c r="C189" s="4" t="n">
         <v>46307</v>
@@ -49652,16 +49676,16 @@
     </row>
     <row r="190">
       <c r="A190" s="4" t="n">
-        <v>44875</v>
+        <v>44893</v>
       </c>
       <c r="B190" s="4" t="n">
-        <v>44883</v>
+        <v>44895</v>
       </c>
       <c r="C190" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D190" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -49671,16 +49695,16 @@
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
-        <v>44866</v>
+        <v>44884</v>
       </c>
       <c r="B191" s="4" t="n">
-        <v>44874</v>
+        <v>44892</v>
       </c>
       <c r="C191" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D191" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -49690,16 +49714,16 @@
     </row>
     <row r="192">
       <c r="A192" s="4" t="n">
-        <v>44862</v>
+        <v>44875</v>
       </c>
       <c r="B192" s="4" t="n">
-        <v>44865</v>
+        <v>44883</v>
       </c>
       <c r="C192" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D192" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -49709,10 +49733,10 @@
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
-        <v>44853</v>
+        <v>44866</v>
       </c>
       <c r="B193" s="4" t="n">
-        <v>44861</v>
+        <v>44874</v>
       </c>
       <c r="C193" s="4" t="n">
         <v>46307</v>
@@ -49728,16 +49752,16 @@
     </row>
     <row r="194">
       <c r="A194" s="4" t="n">
-        <v>44844</v>
+        <v>44862</v>
       </c>
       <c r="B194" s="4" t="n">
-        <v>44852</v>
+        <v>44865</v>
       </c>
       <c r="C194" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D194" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -49747,16 +49771,16 @@
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
-        <v>44835</v>
+        <v>44853</v>
       </c>
       <c r="B195" s="4" t="n">
-        <v>44843</v>
+        <v>44861</v>
       </c>
       <c r="C195" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D195" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -49766,16 +49790,16 @@
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
-        <v>44832</v>
+        <v>44844</v>
       </c>
       <c r="B196" s="4" t="n">
-        <v>44834</v>
+        <v>44852</v>
       </c>
       <c r="C196" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -49785,10 +49809,10 @@
     </row>
     <row r="197">
       <c r="A197" s="4" t="n">
-        <v>44823</v>
+        <v>44835</v>
       </c>
       <c r="B197" s="4" t="n">
-        <v>44831</v>
+        <v>44843</v>
       </c>
       <c r="C197" s="4" t="n">
         <v>46307</v>
@@ -49804,16 +49828,16 @@
     </row>
     <row r="198">
       <c r="A198" s="4" t="n">
-        <v>44814</v>
+        <v>44832</v>
       </c>
       <c r="B198" s="4" t="n">
-        <v>44822</v>
+        <v>44834</v>
       </c>
       <c r="C198" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D198" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -49823,16 +49847,16 @@
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
-        <v>44805</v>
+        <v>44823</v>
       </c>
       <c r="B199" s="4" t="n">
-        <v>44813</v>
+        <v>44831</v>
       </c>
       <c r="C199" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D199" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -49842,16 +49866,16 @@
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
-        <v>44801</v>
+        <v>44814</v>
       </c>
       <c r="B200" s="4" t="n">
-        <v>44804</v>
+        <v>44822</v>
       </c>
       <c r="C200" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D200" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -49861,16 +49885,16 @@
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
-        <v>44792</v>
+        <v>44805</v>
       </c>
       <c r="B201" s="4" t="n">
-        <v>44800</v>
+        <v>44813</v>
       </c>
       <c r="C201" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D201" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -49880,16 +49904,16 @@
     </row>
     <row r="202">
       <c r="A202" s="4" t="n">
-        <v>44783</v>
+        <v>44801</v>
       </c>
       <c r="B202" s="4" t="n">
-        <v>44791</v>
+        <v>44804</v>
       </c>
       <c r="C202" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D202" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -49899,10 +49923,10 @@
     </row>
     <row r="203">
       <c r="A203" s="4" t="n">
-        <v>44774</v>
+        <v>44792</v>
       </c>
       <c r="B203" s="4" t="n">
-        <v>44782</v>
+        <v>44800</v>
       </c>
       <c r="C203" s="4" t="n">
         <v>46307</v>
@@ -49918,16 +49942,16 @@
     </row>
     <row r="204">
       <c r="A204" s="4" t="n">
-        <v>44770</v>
+        <v>44783</v>
       </c>
       <c r="B204" s="4" t="n">
-        <v>44773</v>
+        <v>44791</v>
       </c>
       <c r="C204" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -49937,10 +49961,10 @@
     </row>
     <row r="205">
       <c r="A205" s="4" t="n">
-        <v>44761</v>
+        <v>44774</v>
       </c>
       <c r="B205" s="4" t="n">
-        <v>44769</v>
+        <v>44782</v>
       </c>
       <c r="C205" s="4" t="n">
         <v>46307</v>
@@ -49956,16 +49980,16 @@
     </row>
     <row r="206">
       <c r="A206" s="4" t="n">
-        <v>44752</v>
+        <v>44770</v>
       </c>
       <c r="B206" s="4" t="n">
-        <v>44760</v>
+        <v>44773</v>
       </c>
       <c r="C206" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D206" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -49975,16 +49999,16 @@
     </row>
     <row r="207">
       <c r="A207" s="4" t="n">
-        <v>44743</v>
+        <v>44761</v>
       </c>
       <c r="B207" s="4" t="n">
-        <v>44751</v>
+        <v>44769</v>
       </c>
       <c r="C207" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D207" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -49994,16 +50018,16 @@
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
-        <v>44740</v>
+        <v>44752</v>
       </c>
       <c r="B208" s="4" t="n">
-        <v>44742</v>
+        <v>44760</v>
       </c>
       <c r="C208" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -50013,10 +50037,10 @@
     </row>
     <row r="209">
       <c r="A209" s="4" t="n">
-        <v>44731</v>
+        <v>44743</v>
       </c>
       <c r="B209" s="4" t="n">
-        <v>44739</v>
+        <v>44751</v>
       </c>
       <c r="C209" s="4" t="n">
         <v>46307</v>
@@ -50032,16 +50056,16 @@
     </row>
     <row r="210">
       <c r="A210" s="4" t="n">
-        <v>44722</v>
+        <v>44740</v>
       </c>
       <c r="B210" s="4" t="n">
-        <v>44730</v>
+        <v>44742</v>
       </c>
       <c r="C210" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D210" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -50051,16 +50075,16 @@
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
-        <v>44713</v>
+        <v>44731</v>
       </c>
       <c r="B211" s="4" t="n">
-        <v>44721</v>
+        <v>44739</v>
       </c>
       <c r="C211" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D211" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -50070,16 +50094,16 @@
     </row>
     <row r="212">
       <c r="A212" s="4" t="n">
-        <v>44709</v>
+        <v>44722</v>
       </c>
       <c r="B212" s="4" t="n">
-        <v>44712</v>
+        <v>44730</v>
       </c>
       <c r="C212" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -50089,16 +50113,16 @@
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
-        <v>44700</v>
+        <v>44713</v>
       </c>
       <c r="B213" s="4" t="n">
-        <v>44708</v>
+        <v>44721</v>
       </c>
       <c r="C213" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D213" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -50108,16 +50132,16 @@
     </row>
     <row r="214">
       <c r="A214" s="4" t="n">
-        <v>44691</v>
+        <v>44709</v>
       </c>
       <c r="B214" s="4" t="n">
-        <v>44699</v>
+        <v>44712</v>
       </c>
       <c r="C214" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D214" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -50127,10 +50151,10 @@
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
-        <v>44682</v>
+        <v>44700</v>
       </c>
       <c r="B215" s="4" t="n">
-        <v>44690</v>
+        <v>44708</v>
       </c>
       <c r="C215" s="4" t="n">
         <v>46307</v>
@@ -50146,16 +50170,16 @@
     </row>
     <row r="216">
       <c r="A216" s="4" t="n">
-        <v>44679</v>
+        <v>44691</v>
       </c>
       <c r="B216" s="4" t="n">
-        <v>44681</v>
+        <v>44699</v>
       </c>
       <c r="C216" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D216" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -50165,16 +50189,16 @@
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
-        <v>44670</v>
+        <v>44682</v>
       </c>
       <c r="B217" s="4" t="n">
-        <v>44678</v>
+        <v>44690</v>
       </c>
       <c r="C217" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D217" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -50184,16 +50208,16 @@
     </row>
     <row r="218">
       <c r="A218" s="4" t="n">
-        <v>44661</v>
+        <v>44679</v>
       </c>
       <c r="B218" s="4" t="n">
-        <v>44669</v>
+        <v>44681</v>
       </c>
       <c r="C218" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D218" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -50203,10 +50227,10 @@
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
-        <v>44652</v>
+        <v>44670</v>
       </c>
       <c r="B219" s="4" t="n">
-        <v>44660</v>
+        <v>44678</v>
       </c>
       <c r="C219" s="4" t="n">
         <v>46307</v>
@@ -50222,16 +50246,16 @@
     </row>
     <row r="220">
       <c r="A220" s="4" t="n">
-        <v>44648</v>
+        <v>44661</v>
       </c>
       <c r="B220" s="4" t="n">
-        <v>44651</v>
+        <v>44669</v>
       </c>
       <c r="C220" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -50241,16 +50265,16 @@
     </row>
     <row r="221">
       <c r="A221" s="4" t="n">
-        <v>44639</v>
+        <v>44652</v>
       </c>
       <c r="B221" s="4" t="n">
-        <v>44647</v>
+        <v>44660</v>
       </c>
       <c r="C221" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D221" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -50260,16 +50284,16 @@
     </row>
     <row r="222">
       <c r="A222" s="4" t="n">
-        <v>44630</v>
+        <v>44648</v>
       </c>
       <c r="B222" s="4" t="n">
-        <v>44638</v>
+        <v>44651</v>
       </c>
       <c r="C222" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D222" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -50279,16 +50303,16 @@
     </row>
     <row r="223">
       <c r="A223" s="4" t="n">
-        <v>44621</v>
+        <v>44639</v>
       </c>
       <c r="B223" s="4" t="n">
-        <v>44629</v>
+        <v>44647</v>
       </c>
       <c r="C223" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D223" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -50298,16 +50322,16 @@
     </row>
     <row r="224">
       <c r="A224" s="4" t="n">
-        <v>44620</v>
+        <v>44630</v>
       </c>
       <c r="B224" s="4" t="n">
-        <v>44620</v>
+        <v>44638</v>
       </c>
       <c r="C224" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -50317,16 +50341,16 @@
     </row>
     <row r="225">
       <c r="A225" s="4" t="n">
-        <v>44611</v>
+        <v>44621</v>
       </c>
       <c r="B225" s="4" t="n">
-        <v>44619</v>
+        <v>44629</v>
       </c>
       <c r="C225" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D225" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -50336,16 +50360,16 @@
     </row>
     <row r="226">
       <c r="A226" s="4" t="n">
-        <v>44602</v>
+        <v>44620</v>
       </c>
       <c r="B226" s="4" t="n">
-        <v>44610</v>
+        <v>44620</v>
       </c>
       <c r="C226" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D226" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -50355,16 +50379,16 @@
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
-        <v>44593</v>
+        <v>44611</v>
       </c>
       <c r="B227" s="4" t="n">
-        <v>44601</v>
+        <v>44619</v>
       </c>
       <c r="C227" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D227" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -50374,16 +50398,16 @@
     </row>
     <row r="228">
       <c r="A228" s="4" t="n">
-        <v>44589</v>
+        <v>44602</v>
       </c>
       <c r="B228" s="4" t="n">
-        <v>44592</v>
+        <v>44610</v>
       </c>
       <c r="C228" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D228" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -50393,16 +50417,16 @@
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
-        <v>44580</v>
+        <v>44593</v>
       </c>
       <c r="B229" s="4" t="n">
-        <v>44588</v>
+        <v>44601</v>
       </c>
       <c r="C229" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D229" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -50412,16 +50436,16 @@
     </row>
     <row r="230">
       <c r="A230" s="4" t="n">
-        <v>44571</v>
+        <v>44589</v>
       </c>
       <c r="B230" s="4" t="n">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C230" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D230" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -50431,16 +50455,16 @@
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
-        <v>44562</v>
+        <v>44580</v>
       </c>
       <c r="B231" s="4" t="n">
-        <v>44570</v>
+        <v>44588</v>
       </c>
       <c r="C231" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D231" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -50450,16 +50474,16 @@
     </row>
     <row r="232">
       <c r="A232" s="4" t="n">
-        <v>44558</v>
+        <v>44571</v>
       </c>
       <c r="B232" s="4" t="n">
-        <v>44561</v>
+        <v>44579</v>
       </c>
       <c r="C232" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D232" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -50469,16 +50493,16 @@
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
-        <v>44549</v>
+        <v>44562</v>
       </c>
       <c r="B233" s="4" t="n">
-        <v>44557</v>
+        <v>44570</v>
       </c>
       <c r="C233" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D233" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -50488,16 +50512,16 @@
     </row>
     <row r="234">
       <c r="A234" s="4" t="n">
-        <v>44540</v>
+        <v>44558</v>
       </c>
       <c r="B234" s="4" t="n">
-        <v>44548</v>
+        <v>44561</v>
       </c>
       <c r="C234" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D234" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -50507,16 +50531,16 @@
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
-        <v>44531</v>
+        <v>44549</v>
       </c>
       <c r="B235" s="4" t="n">
-        <v>44539</v>
+        <v>44557</v>
       </c>
       <c r="C235" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D235" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -50526,16 +50550,16 @@
     </row>
     <row r="236">
       <c r="A236" s="4" t="n">
-        <v>44528</v>
+        <v>44540</v>
       </c>
       <c r="B236" s="4" t="n">
-        <v>44530</v>
+        <v>44548</v>
       </c>
       <c r="C236" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D236" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -50545,16 +50569,16 @@
     </row>
     <row r="237">
       <c r="A237" s="4" t="n">
-        <v>44519</v>
+        <v>44531</v>
       </c>
       <c r="B237" s="4" t="n">
-        <v>44527</v>
+        <v>44539</v>
       </c>
       <c r="C237" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D237" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -50564,16 +50588,16 @@
     </row>
     <row r="238">
       <c r="A238" s="4" t="n">
-        <v>44510</v>
+        <v>44528</v>
       </c>
       <c r="B238" s="4" t="n">
-        <v>44518</v>
+        <v>44530</v>
       </c>
       <c r="C238" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D238" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -50583,16 +50607,16 @@
     </row>
     <row r="239">
       <c r="A239" s="4" t="n">
-        <v>44501</v>
+        <v>44519</v>
       </c>
       <c r="B239" s="4" t="n">
-        <v>44509</v>
+        <v>44527</v>
       </c>
       <c r="C239" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D239" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -50602,16 +50626,16 @@
     </row>
     <row r="240">
       <c r="A240" s="4" t="n">
-        <v>44497</v>
+        <v>44510</v>
       </c>
       <c r="B240" s="4" t="n">
-        <v>44500</v>
+        <v>44518</v>
       </c>
       <c r="C240" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D240" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -50621,16 +50645,16 @@
     </row>
     <row r="241">
       <c r="A241" s="4" t="n">
-        <v>44488</v>
+        <v>44501</v>
       </c>
       <c r="B241" s="4" t="n">
-        <v>44496</v>
+        <v>44509</v>
       </c>
       <c r="C241" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D241" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -50640,16 +50664,16 @@
     </row>
     <row r="242">
       <c r="A242" s="4" t="n">
-        <v>44479</v>
+        <v>44497</v>
       </c>
       <c r="B242" s="4" t="n">
-        <v>44487</v>
+        <v>44500</v>
       </c>
       <c r="C242" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D242" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -50659,10 +50683,10 @@
     </row>
     <row r="243">
       <c r="A243" s="4" t="n">
-        <v>44470</v>
+        <v>44488</v>
       </c>
       <c r="B243" s="4" t="n">
-        <v>44478</v>
+        <v>44496</v>
       </c>
       <c r="C243" s="4" t="n">
         <v>46307</v>
@@ -50678,16 +50702,16 @@
     </row>
     <row r="244">
       <c r="A244" s="4" t="n">
-        <v>44467</v>
+        <v>44479</v>
       </c>
       <c r="B244" s="4" t="n">
-        <v>44469</v>
+        <v>44487</v>
       </c>
       <c r="C244" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D244" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -50697,16 +50721,16 @@
     </row>
     <row r="245">
       <c r="A245" s="4" t="n">
-        <v>44458</v>
+        <v>44470</v>
       </c>
       <c r="B245" s="4" t="n">
-        <v>44466</v>
+        <v>44478</v>
       </c>
       <c r="C245" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D245" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -50716,16 +50740,16 @@
     </row>
     <row r="246">
       <c r="A246" s="4" t="n">
-        <v>44449</v>
+        <v>44467</v>
       </c>
       <c r="B246" s="4" t="n">
-        <v>44457</v>
+        <v>44469</v>
       </c>
       <c r="C246" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D246" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -50735,16 +50759,16 @@
     </row>
     <row r="247">
       <c r="A247" s="4" t="n">
-        <v>44440</v>
+        <v>44458</v>
       </c>
       <c r="B247" s="4" t="n">
-        <v>44448</v>
+        <v>44466</v>
       </c>
       <c r="C247" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D247" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -50754,16 +50778,16 @@
     </row>
     <row r="248">
       <c r="A248" s="4" t="n">
-        <v>44436</v>
+        <v>44449</v>
       </c>
       <c r="B248" s="4" t="n">
-        <v>44439</v>
+        <v>44457</v>
       </c>
       <c r="C248" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D248" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -50773,16 +50797,16 @@
     </row>
     <row r="249">
       <c r="A249" s="4" t="n">
-        <v>44427</v>
+        <v>44440</v>
       </c>
       <c r="B249" s="4" t="n">
-        <v>44435</v>
+        <v>44448</v>
       </c>
       <c r="C249" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D249" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -50792,16 +50816,16 @@
     </row>
     <row r="250">
       <c r="A250" s="4" t="n">
-        <v>44418</v>
+        <v>44436</v>
       </c>
       <c r="B250" s="4" t="n">
-        <v>44426</v>
+        <v>44439</v>
       </c>
       <c r="C250" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D250" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -50811,10 +50835,10 @@
     </row>
     <row r="251">
       <c r="A251" s="4" t="n">
-        <v>44409</v>
+        <v>44427</v>
       </c>
       <c r="B251" s="4" t="n">
-        <v>44417</v>
+        <v>44435</v>
       </c>
       <c r="C251" s="4" t="n">
         <v>46307</v>
@@ -50830,16 +50854,16 @@
     </row>
     <row r="252">
       <c r="A252" s="4" t="n">
-        <v>44405</v>
+        <v>44418</v>
       </c>
       <c r="B252" s="4" t="n">
-        <v>44408</v>
+        <v>44426</v>
       </c>
       <c r="C252" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D252" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -50849,10 +50873,10 @@
     </row>
     <row r="253">
       <c r="A253" s="4" t="n">
-        <v>44396</v>
+        <v>44409</v>
       </c>
       <c r="B253" s="4" t="n">
-        <v>44404</v>
+        <v>44417</v>
       </c>
       <c r="C253" s="4" t="n">
         <v>46307</v>
@@ -50868,16 +50892,16 @@
     </row>
     <row r="254">
       <c r="A254" s="4" t="n">
-        <v>44387</v>
+        <v>44405</v>
       </c>
       <c r="B254" s="4" t="n">
-        <v>44395</v>
+        <v>44408</v>
       </c>
       <c r="C254" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D254" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -50887,10 +50911,10 @@
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
-        <v>44378</v>
+        <v>44396</v>
       </c>
       <c r="B255" s="4" t="n">
-        <v>44386</v>
+        <v>44404</v>
       </c>
       <c r="C255" s="4" t="n">
         <v>46307</v>
@@ -50906,16 +50930,16 @@
     </row>
     <row r="256">
       <c r="A256" s="4" t="n">
-        <v>44375</v>
+        <v>44387</v>
       </c>
       <c r="B256" s="4" t="n">
-        <v>44377</v>
+        <v>44395</v>
       </c>
       <c r="C256" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -50925,10 +50949,10 @@
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
-        <v>44366</v>
+        <v>44378</v>
       </c>
       <c r="B257" s="4" t="n">
-        <v>44374</v>
+        <v>44386</v>
       </c>
       <c r="C257" s="4" t="n">
         <v>46307</v>
@@ -50944,16 +50968,16 @@
     </row>
     <row r="258">
       <c r="A258" s="4" t="n">
-        <v>44357</v>
+        <v>44375</v>
       </c>
       <c r="B258" s="4" t="n">
-        <v>44365</v>
+        <v>44377</v>
       </c>
       <c r="C258" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D258" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -50963,16 +50987,16 @@
     </row>
     <row r="259">
       <c r="A259" s="4" t="n">
-        <v>44348</v>
+        <v>44366</v>
       </c>
       <c r="B259" s="4" t="n">
-        <v>44356</v>
+        <v>44374</v>
       </c>
       <c r="C259" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D259" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -50982,16 +51006,16 @@
     </row>
     <row r="260">
       <c r="A260" s="4" t="n">
-        <v>44344</v>
+        <v>44357</v>
       </c>
       <c r="B260" s="4" t="n">
-        <v>44347</v>
+        <v>44365</v>
       </c>
       <c r="C260" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D260" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -51001,10 +51025,10 @@
     </row>
     <row r="261">
       <c r="A261" s="4" t="n">
-        <v>44335</v>
+        <v>44348</v>
       </c>
       <c r="B261" s="4" t="n">
-        <v>44343</v>
+        <v>44356</v>
       </c>
       <c r="C261" s="4" t="n">
         <v>46307</v>
@@ -51020,16 +51044,16 @@
     </row>
     <row r="262">
       <c r="A262" s="4" t="n">
-        <v>44326</v>
+        <v>44344</v>
       </c>
       <c r="B262" s="4" t="n">
-        <v>44334</v>
+        <v>44347</v>
       </c>
       <c r="C262" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D262" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -51039,16 +51063,16 @@
     </row>
     <row r="263">
       <c r="A263" s="4" t="n">
-        <v>44317</v>
+        <v>44335</v>
       </c>
       <c r="B263" s="4" t="n">
-        <v>44325</v>
+        <v>44343</v>
       </c>
       <c r="C263" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D263" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -51058,16 +51082,16 @@
     </row>
     <row r="264">
       <c r="A264" s="4" t="n">
-        <v>44314</v>
+        <v>44326</v>
       </c>
       <c r="B264" s="4" t="n">
-        <v>44316</v>
+        <v>44334</v>
       </c>
       <c r="C264" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D264" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -51077,10 +51101,10 @@
     </row>
     <row r="265">
       <c r="A265" s="4" t="n">
-        <v>44305</v>
+        <v>44317</v>
       </c>
       <c r="B265" s="4" t="n">
-        <v>44313</v>
+        <v>44325</v>
       </c>
       <c r="C265" s="4" t="n">
         <v>46307</v>
@@ -51096,16 +51120,16 @@
     </row>
     <row r="266">
       <c r="A266" s="4" t="n">
-        <v>44296</v>
+        <v>44314</v>
       </c>
       <c r="B266" s="4" t="n">
-        <v>44304</v>
+        <v>44316</v>
       </c>
       <c r="C266" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D266" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -51115,16 +51139,16 @@
     </row>
     <row r="267">
       <c r="A267" s="4" t="n">
-        <v>44287</v>
+        <v>44305</v>
       </c>
       <c r="B267" s="4" t="n">
-        <v>44295</v>
+        <v>44313</v>
       </c>
       <c r="C267" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D267" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -51134,16 +51158,16 @@
     </row>
     <row r="268">
       <c r="A268" s="4" t="n">
-        <v>44283</v>
+        <v>44296</v>
       </c>
       <c r="B268" s="4" t="n">
-        <v>44286</v>
+        <v>44304</v>
       </c>
       <c r="C268" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D268" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -51153,10 +51177,10 @@
     </row>
     <row r="269">
       <c r="A269" s="4" t="n">
-        <v>44274</v>
+        <v>44287</v>
       </c>
       <c r="B269" s="4" t="n">
-        <v>44282</v>
+        <v>44295</v>
       </c>
       <c r="C269" s="4" t="n">
         <v>46307</v>
@@ -51172,16 +51196,16 @@
     </row>
     <row r="270">
       <c r="A270" s="4" t="n">
-        <v>44265</v>
+        <v>44283</v>
       </c>
       <c r="B270" s="4" t="n">
-        <v>44273</v>
+        <v>44286</v>
       </c>
       <c r="C270" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D270" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -51191,10 +51215,10 @@
     </row>
     <row r="271">
       <c r="A271" s="4" t="n">
-        <v>44256</v>
+        <v>44274</v>
       </c>
       <c r="B271" s="4" t="n">
-        <v>44264</v>
+        <v>44282</v>
       </c>
       <c r="C271" s="4" t="n">
         <v>46307</v>
@@ -51210,16 +51234,16 @@
     </row>
     <row r="272">
       <c r="A272" s="4" t="n">
-        <v>44255</v>
+        <v>44265</v>
       </c>
       <c r="B272" s="4" t="n">
-        <v>44255</v>
+        <v>44273</v>
       </c>
       <c r="C272" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -51229,16 +51253,16 @@
     </row>
     <row r="273">
       <c r="A273" s="4" t="n">
-        <v>44246</v>
+        <v>44256</v>
       </c>
       <c r="B273" s="4" t="n">
-        <v>44254</v>
+        <v>44264</v>
       </c>
       <c r="C273" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D273" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -51248,16 +51272,16 @@
     </row>
     <row r="274">
       <c r="A274" s="4" t="n">
-        <v>44237</v>
+        <v>44255</v>
       </c>
       <c r="B274" s="4" t="n">
-        <v>44245</v>
+        <v>44255</v>
       </c>
       <c r="C274" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D274" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -51267,16 +51291,16 @@
     </row>
     <row r="275">
       <c r="A275" s="4" t="n">
-        <v>44228</v>
+        <v>44246</v>
       </c>
       <c r="B275" s="4" t="n">
-        <v>44236</v>
+        <v>44254</v>
       </c>
       <c r="C275" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -51286,16 +51310,16 @@
     </row>
     <row r="276">
       <c r="A276" s="4" t="n">
-        <v>44224</v>
+        <v>44237</v>
       </c>
       <c r="B276" s="4" t="n">
-        <v>44227</v>
+        <v>44245</v>
       </c>
       <c r="C276" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -51305,16 +51329,16 @@
     </row>
     <row r="277">
       <c r="A277" s="4" t="n">
-        <v>44215</v>
+        <v>44228</v>
       </c>
       <c r="B277" s="4" t="n">
-        <v>44223</v>
+        <v>44236</v>
       </c>
       <c r="C277" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D277" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -51324,16 +51348,16 @@
     </row>
     <row r="278">
       <c r="A278" s="4" t="n">
-        <v>44206</v>
+        <v>44224</v>
       </c>
       <c r="B278" s="4" t="n">
-        <v>44214</v>
+        <v>44227</v>
       </c>
       <c r="C278" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D278" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -51343,16 +51367,16 @@
     </row>
     <row r="279">
       <c r="A279" s="4" t="n">
-        <v>44197</v>
+        <v>44215</v>
       </c>
       <c r="B279" s="4" t="n">
-        <v>44205</v>
+        <v>44223</v>
       </c>
       <c r="C279" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -51362,16 +51386,16 @@
     </row>
     <row r="280">
       <c r="A280" s="4" t="n">
-        <v>44193</v>
+        <v>44206</v>
       </c>
       <c r="B280" s="4" t="n">
-        <v>44196</v>
+        <v>44214</v>
       </c>
       <c r="C280" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -51381,16 +51405,16 @@
     </row>
     <row r="281">
       <c r="A281" s="4" t="n">
-        <v>44184</v>
+        <v>44197</v>
       </c>
       <c r="B281" s="4" t="n">
-        <v>44192</v>
+        <v>44205</v>
       </c>
       <c r="C281" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D281" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -51400,16 +51424,16 @@
     </row>
     <row r="282">
       <c r="A282" s="4" t="n">
-        <v>44175</v>
+        <v>44193</v>
       </c>
       <c r="B282" s="4" t="n">
-        <v>44183</v>
+        <v>44196</v>
       </c>
       <c r="C282" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D282" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -51419,16 +51443,16 @@
     </row>
     <row r="283">
       <c r="A283" s="4" t="n">
-        <v>44166</v>
+        <v>44184</v>
       </c>
       <c r="B283" s="4" t="n">
-        <v>44174</v>
+        <v>44192</v>
       </c>
       <c r="C283" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D283" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -51438,29 +51462,29 @@
     </row>
     <row r="284">
       <c r="A284" s="4" t="n">
-        <v>44163</v>
+        <v>44175</v>
       </c>
       <c r="B284" s="4" t="n">
-        <v>44165</v>
+        <v>44183</v>
       </c>
       <c r="C284" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n">
-        <v>44154</v>
+        <v>44166</v>
       </c>
       <c r="B285" s="4" t="n">
-        <v>44162</v>
+        <v>44174</v>
       </c>
       <c r="C285" s="4" t="n">
         <v>46307</v>
@@ -51476,35 +51500,35 @@
     </row>
     <row r="286">
       <c r="A286" s="4" t="n">
-        <v>44145</v>
+        <v>44163</v>
       </c>
       <c r="B286" s="4" t="n">
-        <v>44153</v>
+        <v>44165</v>
       </c>
       <c r="C286" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D286" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n">
-        <v>44136</v>
+        <v>44154</v>
       </c>
       <c r="B287" s="4" t="n">
-        <v>44144</v>
+        <v>44162</v>
       </c>
       <c r="C287" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -51514,35 +51538,35 @@
     </row>
     <row r="288">
       <c r="A288" s="4" t="n">
-        <v>44132</v>
+        <v>44145</v>
       </c>
       <c r="B288" s="4" t="n">
-        <v>44135</v>
+        <v>44153</v>
       </c>
       <c r="C288" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n">
-        <v>44123</v>
+        <v>44136</v>
       </c>
       <c r="B289" s="4" t="n">
-        <v>44131</v>
+        <v>44144</v>
       </c>
       <c r="C289" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D289" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -51552,35 +51576,35 @@
     </row>
     <row r="290">
       <c r="A290" s="4" t="n">
-        <v>44114</v>
+        <v>44132</v>
       </c>
       <c r="B290" s="4" t="n">
-        <v>44122</v>
+        <v>44135</v>
       </c>
       <c r="C290" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D290" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n">
-        <v>44105</v>
+        <v>44123</v>
       </c>
       <c r="B291" s="4" t="n">
-        <v>44113</v>
+        <v>44131</v>
       </c>
       <c r="C291" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D291" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -51590,16 +51614,16 @@
     </row>
     <row r="292">
       <c r="A292" s="4" t="n">
-        <v>44102</v>
+        <v>44114</v>
       </c>
       <c r="B292" s="4" t="n">
-        <v>44104</v>
+        <v>44122</v>
       </c>
       <c r="C292" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D292" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -51609,10 +51633,10 @@
     </row>
     <row r="293">
       <c r="A293" s="4" t="n">
-        <v>44093</v>
+        <v>44105</v>
       </c>
       <c r="B293" s="4" t="n">
-        <v>44101</v>
+        <v>44113</v>
       </c>
       <c r="C293" s="4" t="n">
         <v>46307</v>
@@ -51628,16 +51652,16 @@
     </row>
     <row r="294">
       <c r="A294" s="4" t="n">
-        <v>44084</v>
+        <v>44102</v>
       </c>
       <c r="B294" s="4" t="n">
-        <v>44092</v>
+        <v>44104</v>
       </c>
       <c r="C294" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -51647,16 +51671,16 @@
     </row>
     <row r="295">
       <c r="A295" s="4" t="n">
-        <v>44075</v>
+        <v>44093</v>
       </c>
       <c r="B295" s="4" t="n">
-        <v>44083</v>
+        <v>44101</v>
       </c>
       <c r="C295" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -51666,10 +51690,10 @@
     </row>
     <row r="296">
       <c r="A296" s="4" t="n">
-        <v>44071</v>
+        <v>44084</v>
       </c>
       <c r="B296" s="4" t="n">
-        <v>44074</v>
+        <v>44092</v>
       </c>
       <c r="C296" s="4" t="n">
         <v>46307</v>
@@ -51685,16 +51709,16 @@
     </row>
     <row r="297">
       <c r="A297" s="4" t="n">
-        <v>44062</v>
+        <v>44075</v>
       </c>
       <c r="B297" s="4" t="n">
-        <v>44070</v>
+        <v>44083</v>
       </c>
       <c r="C297" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D297" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -51704,16 +51728,16 @@
     </row>
     <row r="298">
       <c r="A298" s="4" t="n">
-        <v>44053</v>
+        <v>44071</v>
       </c>
       <c r="B298" s="4" t="n">
-        <v>44061</v>
+        <v>44074</v>
       </c>
       <c r="C298" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D298" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -51723,16 +51747,16 @@
     </row>
     <row r="299">
       <c r="A299" s="4" t="n">
-        <v>44044</v>
+        <v>44062</v>
       </c>
       <c r="B299" s="4" t="n">
-        <v>44052</v>
+        <v>44070</v>
       </c>
       <c r="C299" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -51742,16 +51766,16 @@
     </row>
     <row r="300">
       <c r="A300" s="4" t="n">
-        <v>44040</v>
+        <v>44053</v>
       </c>
       <c r="B300" s="4" t="n">
-        <v>44043</v>
+        <v>44061</v>
       </c>
       <c r="C300" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D300" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -51761,16 +51785,16 @@
     </row>
     <row r="301">
       <c r="A301" s="4" t="n">
-        <v>44031</v>
+        <v>44044</v>
       </c>
       <c r="B301" s="4" t="n">
-        <v>44039</v>
+        <v>44052</v>
       </c>
       <c r="C301" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D301" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -51780,16 +51804,16 @@
     </row>
     <row r="302">
       <c r="A302" s="4" t="n">
-        <v>44022</v>
+        <v>44040</v>
       </c>
       <c r="B302" s="4" t="n">
-        <v>44030</v>
+        <v>44043</v>
       </c>
       <c r="C302" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D302" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -51799,10 +51823,10 @@
     </row>
     <row r="303">
       <c r="A303" s="4" t="n">
-        <v>44013</v>
+        <v>44031</v>
       </c>
       <c r="B303" s="4" t="n">
-        <v>44021</v>
+        <v>44039</v>
       </c>
       <c r="C303" s="4" t="n">
         <v>46307</v>
@@ -51818,16 +51842,16 @@
     </row>
     <row r="304">
       <c r="A304" s="4" t="n">
-        <v>44010</v>
+        <v>44022</v>
       </c>
       <c r="B304" s="4" t="n">
-        <v>44012</v>
+        <v>44030</v>
       </c>
       <c r="C304" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -51837,16 +51861,16 @@
     </row>
     <row r="305">
       <c r="A305" s="4" t="n">
-        <v>44001</v>
+        <v>44013</v>
       </c>
       <c r="B305" s="4" t="n">
-        <v>44009</v>
+        <v>44021</v>
       </c>
       <c r="C305" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D305" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -51856,16 +51880,16 @@
     </row>
     <row r="306">
       <c r="A306" s="4" t="n">
-        <v>43992</v>
+        <v>44010</v>
       </c>
       <c r="B306" s="4" t="n">
-        <v>44000</v>
+        <v>44012</v>
       </c>
       <c r="C306" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D306" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -51875,16 +51899,16 @@
     </row>
     <row r="307">
       <c r="A307" s="4" t="n">
-        <v>43983</v>
+        <v>44001</v>
       </c>
       <c r="B307" s="4" t="n">
-        <v>43991</v>
+        <v>44009</v>
       </c>
       <c r="C307" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D307" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -51894,16 +51918,16 @@
     </row>
     <row r="308">
       <c r="A308" s="4" t="n">
-        <v>43979</v>
+        <v>43992</v>
       </c>
       <c r="B308" s="4" t="n">
-        <v>43982</v>
+        <v>44000</v>
       </c>
       <c r="C308" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D308" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -51913,16 +51937,16 @@
     </row>
     <row r="309">
       <c r="A309" s="4" t="n">
-        <v>43970</v>
+        <v>43983</v>
       </c>
       <c r="B309" s="4" t="n">
-        <v>43978</v>
+        <v>43991</v>
       </c>
       <c r="C309" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D309" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -51932,16 +51956,16 @@
     </row>
     <row r="310">
       <c r="A310" s="4" t="n">
-        <v>43961</v>
+        <v>43979</v>
       </c>
       <c r="B310" s="4" t="n">
-        <v>43969</v>
+        <v>43982</v>
       </c>
       <c r="C310" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D310" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -51951,10 +51975,10 @@
     </row>
     <row r="311">
       <c r="A311" s="4" t="n">
-        <v>43952</v>
+        <v>43970</v>
       </c>
       <c r="B311" s="4" t="n">
-        <v>43960</v>
+        <v>43978</v>
       </c>
       <c r="C311" s="4" t="n">
         <v>46307</v>
@@ -51970,16 +51994,16 @@
     </row>
     <row r="312">
       <c r="A312" s="4" t="n">
-        <v>43949</v>
+        <v>43961</v>
       </c>
       <c r="B312" s="4" t="n">
-        <v>43951</v>
+        <v>43969</v>
       </c>
       <c r="C312" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D312" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -51989,16 +52013,16 @@
     </row>
     <row r="313">
       <c r="A313" s="4" t="n">
-        <v>43940</v>
+        <v>43952</v>
       </c>
       <c r="B313" s="4" t="n">
-        <v>43948</v>
+        <v>43960</v>
       </c>
       <c r="C313" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D313" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -52008,16 +52032,16 @@
     </row>
     <row r="314">
       <c r="A314" s="4" t="n">
-        <v>43931</v>
+        <v>43949</v>
       </c>
       <c r="B314" s="4" t="n">
-        <v>43939</v>
+        <v>43951</v>
       </c>
       <c r="C314" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D314" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -52027,10 +52051,10 @@
     </row>
     <row r="315">
       <c r="A315" s="4" t="n">
-        <v>43922</v>
+        <v>43940</v>
       </c>
       <c r="B315" s="4" t="n">
-        <v>43930</v>
+        <v>43948</v>
       </c>
       <c r="C315" s="4" t="n">
         <v>46307</v>
@@ -52046,16 +52070,16 @@
     </row>
     <row r="316">
       <c r="A316" s="4" t="n">
-        <v>43918</v>
+        <v>43931</v>
       </c>
       <c r="B316" s="4" t="n">
-        <v>43921</v>
+        <v>43939</v>
       </c>
       <c r="C316" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -52065,16 +52089,16 @@
     </row>
     <row r="317">
       <c r="A317" s="4" t="n">
-        <v>43909</v>
+        <v>43922</v>
       </c>
       <c r="B317" s="4" t="n">
-        <v>43917</v>
+        <v>43930</v>
       </c>
       <c r="C317" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D317" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -52084,16 +52108,16 @@
     </row>
     <row r="318">
       <c r="A318" s="4" t="n">
-        <v>43900</v>
+        <v>43918</v>
       </c>
       <c r="B318" s="4" t="n">
-        <v>43908</v>
+        <v>43921</v>
       </c>
       <c r="C318" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D318" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -52103,16 +52127,16 @@
     </row>
     <row r="319">
       <c r="A319" s="4" t="n">
-        <v>43891</v>
+        <v>43909</v>
       </c>
       <c r="B319" s="4" t="n">
-        <v>43899</v>
+        <v>43917</v>
       </c>
       <c r="C319" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D319" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -52122,35 +52146,35 @@
     </row>
     <row r="320">
       <c r="A320" s="4" t="n">
-        <v>43889</v>
+        <v>43900</v>
       </c>
       <c r="B320" s="4" t="n">
-        <v>43890</v>
+        <v>43908</v>
       </c>
       <c r="C320" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="n">
-        <v>43880</v>
+        <v>43891</v>
       </c>
       <c r="B321" s="4" t="n">
-        <v>43888</v>
+        <v>43899</v>
       </c>
       <c r="C321" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D321" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -52160,35 +52184,35 @@
     </row>
     <row r="322">
       <c r="A322" s="4" t="n">
-        <v>43871</v>
+        <v>43889</v>
       </c>
       <c r="B322" s="4" t="n">
-        <v>43879</v>
+        <v>43890</v>
       </c>
       <c r="C322" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D322" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>empty</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n">
-        <v>43862</v>
+        <v>43880</v>
       </c>
       <c r="B323" s="4" t="n">
-        <v>43870</v>
+        <v>43888</v>
       </c>
       <c r="C323" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D323" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -52198,16 +52222,16 @@
     </row>
     <row r="324">
       <c r="A324" s="4" t="n">
-        <v>43858</v>
+        <v>43871</v>
       </c>
       <c r="B324" s="4" t="n">
-        <v>43861</v>
+        <v>43879</v>
       </c>
       <c r="C324" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -52217,16 +52241,16 @@
     </row>
     <row r="325">
       <c r="A325" s="4" t="n">
-        <v>43849</v>
+        <v>43862</v>
       </c>
       <c r="B325" s="4" t="n">
-        <v>43857</v>
+        <v>43870</v>
       </c>
       <c r="C325" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D325" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -52236,16 +52260,16 @@
     </row>
     <row r="326">
       <c r="A326" s="4" t="n">
-        <v>43840</v>
+        <v>43858</v>
       </c>
       <c r="B326" s="4" t="n">
-        <v>43848</v>
+        <v>43861</v>
       </c>
       <c r="C326" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D326" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -52255,16 +52279,16 @@
     </row>
     <row r="327">
       <c r="A327" s="4" t="n">
-        <v>43831</v>
+        <v>43849</v>
       </c>
       <c r="B327" s="4" t="n">
-        <v>43839</v>
+        <v>43857</v>
       </c>
       <c r="C327" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D327" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -52274,16 +52298,16 @@
     </row>
     <row r="328">
       <c r="A328" s="4" t="n">
-        <v>43827</v>
+        <v>43840</v>
       </c>
       <c r="B328" s="4" t="n">
-        <v>43830</v>
+        <v>43848</v>
       </c>
       <c r="C328" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D328" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -52293,16 +52317,16 @@
     </row>
     <row r="329">
       <c r="A329" s="4" t="n">
-        <v>43818</v>
+        <v>43831</v>
       </c>
       <c r="B329" s="4" t="n">
-        <v>43826</v>
+        <v>43839</v>
       </c>
       <c r="C329" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D329" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -52312,16 +52336,16 @@
     </row>
     <row r="330">
       <c r="A330" s="4" t="n">
-        <v>43809</v>
+        <v>43827</v>
       </c>
       <c r="B330" s="4" t="n">
-        <v>43817</v>
+        <v>43830</v>
       </c>
       <c r="C330" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D330" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -52331,16 +52355,16 @@
     </row>
     <row r="331">
       <c r="A331" s="4" t="n">
-        <v>43800</v>
+        <v>43818</v>
       </c>
       <c r="B331" s="4" t="n">
-        <v>43808</v>
+        <v>43826</v>
       </c>
       <c r="C331" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D331" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -52350,16 +52374,16 @@
     </row>
     <row r="332">
       <c r="A332" s="4" t="n">
-        <v>43797</v>
+        <v>43809</v>
       </c>
       <c r="B332" s="4" t="n">
-        <v>43799</v>
+        <v>43817</v>
       </c>
       <c r="C332" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -52369,10 +52393,10 @@
     </row>
     <row r="333">
       <c r="A333" s="4" t="n">
-        <v>43788</v>
+        <v>43800</v>
       </c>
       <c r="B333" s="4" t="n">
-        <v>43796</v>
+        <v>43808</v>
       </c>
       <c r="C333" s="4" t="n">
         <v>46307</v>
@@ -52388,16 +52412,16 @@
     </row>
     <row r="334">
       <c r="A334" s="4" t="n">
-        <v>43779</v>
+        <v>43797</v>
       </c>
       <c r="B334" s="4" t="n">
-        <v>43787</v>
+        <v>43799</v>
       </c>
       <c r="C334" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D334" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -52407,16 +52431,16 @@
     </row>
     <row r="335">
       <c r="A335" s="4" t="n">
-        <v>43770</v>
+        <v>43788</v>
       </c>
       <c r="B335" s="4" t="n">
-        <v>43778</v>
+        <v>43796</v>
       </c>
       <c r="C335" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D335" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -52426,16 +52450,16 @@
     </row>
     <row r="336">
       <c r="A336" s="4" t="n">
-        <v>43766</v>
+        <v>43779</v>
       </c>
       <c r="B336" s="4" t="n">
-        <v>43769</v>
+        <v>43787</v>
       </c>
       <c r="C336" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D336" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -52445,16 +52469,16 @@
     </row>
     <row r="337">
       <c r="A337" s="4" t="n">
-        <v>43757</v>
+        <v>43770</v>
       </c>
       <c r="B337" s="4" t="n">
-        <v>43765</v>
+        <v>43778</v>
       </c>
       <c r="C337" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D337" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -52464,16 +52488,16 @@
     </row>
     <row r="338">
       <c r="A338" s="4" t="n">
-        <v>43748</v>
+        <v>43766</v>
       </c>
       <c r="B338" s="4" t="n">
-        <v>43756</v>
+        <v>43769</v>
       </c>
       <c r="C338" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D338" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -52483,18 +52507,56 @@
     </row>
     <row r="339">
       <c r="A339" s="4" t="n">
-        <v>43739</v>
+        <v>43757</v>
       </c>
       <c r="B339" s="4" t="n">
-        <v>43747</v>
+        <v>43765</v>
       </c>
       <c r="C339" s="4" t="n">
         <v>46307</v>
       </c>
       <c r="D339" t="n">
+        <v>3</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="n">
+        <v>43748</v>
+      </c>
+      <c r="B340" s="4" t="n">
+        <v>43756</v>
+      </c>
+      <c r="C340" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D340" t="n">
         <v>6</v>
       </c>
-      <c r="E339" t="inlineStr">
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="n">
+        <v>43739</v>
+      </c>
+      <c r="B341" s="4" t="n">
+        <v>43747</v>
+      </c>
+      <c r="C341" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D341" t="n">
+        <v>6</v>
+      </c>
+      <c r="E341" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
